--- a/1_center.xlsx
+++ b/1_center.xlsx
@@ -413,7 +413,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-01 10:44</t>
+    <t>تاريخ التصدير: 2026-03-01 11:54</t>
   </si>
 </sst>
 </file>

--- a/1_center.xlsx
+++ b/1_center.xlsx
@@ -413,7 +413,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-01 11:54</t>
+    <t>تاريخ التصدير: 2026-03-01 12:00</t>
   </si>
 </sst>
 </file>

--- a/1_center.xlsx
+++ b/1_center.xlsx
@@ -413,7 +413,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-01 12:00</t>
+    <t>تاريخ التصدير: 2026-03-01 12:01</t>
   </si>
 </sst>
 </file>

--- a/1_center.xlsx
+++ b/1_center.xlsx
@@ -413,7 +413,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-01 12:01</t>
+    <t>تاريخ التصدير: 2026-03-01 12:05</t>
   </si>
 </sst>
 </file>

--- a/1_center.xlsx
+++ b/1_center.xlsx
@@ -413,7 +413,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-01 12:05</t>
+    <t>تاريخ التصدير: 2026-03-01 12:08</t>
   </si>
 </sst>
 </file>

--- a/1_center.xlsx
+++ b/1_center.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="132">
   <si>
     <t>ناجح ✓</t>
   </si>
@@ -92,10 +92,259 @@
     <t>جودي خالد ابراهيم محمود علي حسن</t>
   </si>
   <si>
-    <t>2026-02-28 15:06</t>
-  </si>
-  <si>
-    <t>20.0%</t>
+    <t>2026-02-28 15:15</t>
+  </si>
+  <si>
+    <t>01030287496</t>
+  </si>
+  <si>
+    <t>Ginakhaled651@gmail.com</t>
+  </si>
+  <si>
+    <t>جينا خالد ابراهيم</t>
+  </si>
+  <si>
+    <t>2026-02-28 17:53</t>
+  </si>
+  <si>
+    <t>80.0%</t>
+  </si>
+  <si>
+    <t>01093005828</t>
+  </si>
+  <si>
+    <t>yreda91099@gmail.com</t>
+  </si>
+  <si>
+    <t>يوسف رضا محمد</t>
+  </si>
+  <si>
+    <t>2026-02-28 15:54</t>
+  </si>
+  <si>
+    <t>01099238981</t>
+  </si>
+  <si>
+    <t>retajshoukry56@gmail.com</t>
+  </si>
+  <si>
+    <t>Retaj shoukry</t>
+  </si>
+  <si>
+    <t>2026-02-28 16:08</t>
+  </si>
+  <si>
+    <t>01009089616</t>
+  </si>
+  <si>
+    <t>malkmahrous20101912@gmail.com</t>
+  </si>
+  <si>
+    <t>Malak Mohamed lotfy</t>
+  </si>
+  <si>
+    <t>2026-02-28 16:14</t>
+  </si>
+  <si>
+    <t>01068201833</t>
+  </si>
+  <si>
+    <t>arwah0984@gmail.com</t>
+  </si>
+  <si>
+    <t>Arwa Hamdy</t>
+  </si>
+  <si>
+    <t>2026-02-28 16:20</t>
+  </si>
+  <si>
+    <t>01014576528</t>
+  </si>
+  <si>
+    <t>tokaam414@gmail.com</t>
+  </si>
+  <si>
+    <t>تقي محمد شحاته</t>
+  </si>
+  <si>
+    <t>2026-02-28 16:17</t>
+  </si>
+  <si>
+    <t>01065645606</t>
+  </si>
+  <si>
+    <t>mohamedahmednagib893@gamil.com</t>
+  </si>
+  <si>
+    <t>Mohamed Ahmed Naguib</t>
+  </si>
+  <si>
+    <t>2026-02-28 17:02</t>
+  </si>
+  <si>
+    <t>01018664991</t>
+  </si>
+  <si>
+    <t>mohannadshaarawy1@gmail.com</t>
+  </si>
+  <si>
+    <t>Mohannad aly shaarawy</t>
+  </si>
+  <si>
+    <t>2026-02-28 16:46</t>
+  </si>
+  <si>
+    <t>01142590154</t>
+  </si>
+  <si>
+    <t>dok.mayarmahmoud@gmail.com</t>
+  </si>
+  <si>
+    <t>Mayar Mahmoud</t>
+  </si>
+  <si>
+    <t>2026-02-28 17:09</t>
+  </si>
+  <si>
+    <t>01552751484</t>
+  </si>
+  <si>
+    <t>saahnosa2010@gmail.com</t>
+  </si>
+  <si>
+    <t>سيف الدين احمد</t>
+  </si>
+  <si>
+    <t>2026-02-28 17:25</t>
+  </si>
+  <si>
+    <t>01202430665</t>
+  </si>
+  <si>
+    <t>alihatemyoussef58@gmail.com</t>
+  </si>
+  <si>
+    <t>Ali Hatem youssef</t>
+  </si>
+  <si>
+    <t>2026-02-28 17:22</t>
+  </si>
+  <si>
+    <t>01063145566</t>
+  </si>
+  <si>
+    <t>Hend95424@gmail.com</t>
+  </si>
+  <si>
+    <t>Hend Amr mohamed</t>
+  </si>
+  <si>
+    <t>01092299968</t>
+  </si>
+  <si>
+    <t>amra90203@gmail.com</t>
+  </si>
+  <si>
+    <t>Ahmed amr farouk</t>
+  </si>
+  <si>
+    <t>2026-02-28 18:03</t>
+  </si>
+  <si>
+    <t>01094047162</t>
+  </si>
+  <si>
+    <t>samehsajeda1@gmail.com</t>
+  </si>
+  <si>
+    <t>ساجده سامح ياقوت</t>
+  </si>
+  <si>
+    <t>2026-02-28 18:02</t>
+  </si>
+  <si>
+    <t>01025448824</t>
+  </si>
+  <si>
+    <t>samaasker41@gmail.com</t>
+  </si>
+  <si>
+    <t>سما</t>
+  </si>
+  <si>
+    <t>2026-02-28 18:33</t>
+  </si>
+  <si>
+    <t>01122210707</t>
+  </si>
+  <si>
+    <t>lamaelshafay67@gmail.com</t>
+  </si>
+  <si>
+    <t>Hªnassameerh</t>
+  </si>
+  <si>
+    <t>2026-02-28 18:41</t>
+  </si>
+  <si>
+    <t>01096959817</t>
+  </si>
+  <si>
+    <t>ahmeddheshamm702@gmail.com</t>
+  </si>
+  <si>
+    <t>محمد هشام جلال</t>
+  </si>
+  <si>
+    <t>2026-02-28 18:36</t>
+  </si>
+  <si>
+    <t>01002426098</t>
+  </si>
+  <si>
+    <t>lujainmohamed194@gmail.com</t>
+  </si>
+  <si>
+    <t>لوجين محمد احمد عبدالغني</t>
+  </si>
+  <si>
+    <t>2026-02-28 19:15</t>
+  </si>
+  <si>
+    <t>01023257949</t>
+  </si>
+  <si>
+    <t>hamza.mohamed.hassan.8800@gmail.com</t>
+  </si>
+  <si>
+    <t>حمزة محمد حسن عبد المقصود</t>
+  </si>
+  <si>
+    <t>2026-02-28 19:17</t>
+  </si>
+  <si>
+    <t>01061456560</t>
+  </si>
+  <si>
+    <t>ahmedtiktok53@gmail.com</t>
+  </si>
+  <si>
+    <t>mariam abo el magd</t>
+  </si>
+  <si>
+    <t>2026-02-28 19:45</t>
+  </si>
+  <si>
+    <t>01125739890</t>
+  </si>
+  <si>
+    <t>oezzat626@gmail.com</t>
+  </si>
+  <si>
+    <t>Omar Mohammed Ezzat</t>
+  </si>
+  <si>
+    <t>2026-03-01 12:27</t>
   </si>
   <si>
     <t>01507270279</t>
@@ -107,258 +356,6 @@
     <t>لوجين</t>
   </si>
   <si>
-    <t>2026-02-28 15:15</t>
-  </si>
-  <si>
-    <t>01030287496</t>
-  </si>
-  <si>
-    <t>Ginakhaled651@gmail.com</t>
-  </si>
-  <si>
-    <t>جينا خالد ابراهيم</t>
-  </si>
-  <si>
-    <t>2026-02-28 17:53</t>
-  </si>
-  <si>
-    <t>80.0%</t>
-  </si>
-  <si>
-    <t>01093005828</t>
-  </si>
-  <si>
-    <t>yreda91099@gmail.com</t>
-  </si>
-  <si>
-    <t>يوسف رضا محمد</t>
-  </si>
-  <si>
-    <t>2026-02-28 15:54</t>
-  </si>
-  <si>
-    <t>01099238981</t>
-  </si>
-  <si>
-    <t>retajshoukry56@gmail.com</t>
-  </si>
-  <si>
-    <t>Retaj shoukry</t>
-  </si>
-  <si>
-    <t>2026-02-28 16:08</t>
-  </si>
-  <si>
-    <t>01009089616</t>
-  </si>
-  <si>
-    <t>malkmahrous20101912@gmail.com</t>
-  </si>
-  <si>
-    <t>Malak Mohamed lotfy</t>
-  </si>
-  <si>
-    <t>2026-02-28 16:14</t>
-  </si>
-  <si>
-    <t>01068201833</t>
-  </si>
-  <si>
-    <t>arwah0984@gmail.com</t>
-  </si>
-  <si>
-    <t>Arwa Hamdy</t>
-  </si>
-  <si>
-    <t>2026-02-28 16:20</t>
-  </si>
-  <si>
-    <t>01014576528</t>
-  </si>
-  <si>
-    <t>tokaam414@gmail.com</t>
-  </si>
-  <si>
-    <t>تقي محمد شحاته</t>
-  </si>
-  <si>
-    <t>2026-02-28 16:17</t>
-  </si>
-  <si>
-    <t>01065645606</t>
-  </si>
-  <si>
-    <t>mohamedahmednagib893@gamil.com</t>
-  </si>
-  <si>
-    <t>Mohamed Ahmed Naguib</t>
-  </si>
-  <si>
-    <t>2026-02-28 17:02</t>
-  </si>
-  <si>
-    <t>01018664991</t>
-  </si>
-  <si>
-    <t>mohannadshaarawy1@gmail.com</t>
-  </si>
-  <si>
-    <t>Mohannad aly shaarawy</t>
-  </si>
-  <si>
-    <t>2026-02-28 16:46</t>
-  </si>
-  <si>
-    <t>01142590154</t>
-  </si>
-  <si>
-    <t>dok.mayarmahmoud@gmail.com</t>
-  </si>
-  <si>
-    <t>Mayar Mahmoud</t>
-  </si>
-  <si>
-    <t>2026-02-28 17:09</t>
-  </si>
-  <si>
-    <t>01552751484</t>
-  </si>
-  <si>
-    <t>saahnosa2010@gmail.com</t>
-  </si>
-  <si>
-    <t>سيف الدين احمد</t>
-  </si>
-  <si>
-    <t>2026-02-28 17:25</t>
-  </si>
-  <si>
-    <t>01202430665</t>
-  </si>
-  <si>
-    <t>alihatemyoussef58@gmail.com</t>
-  </si>
-  <si>
-    <t>Ali Hatem youssef</t>
-  </si>
-  <si>
-    <t>2026-02-28 17:22</t>
-  </si>
-  <si>
-    <t>01063145566</t>
-  </si>
-  <si>
-    <t>Hend95424@gmail.com</t>
-  </si>
-  <si>
-    <t>Hend Amr mohamed</t>
-  </si>
-  <si>
-    <t>01092299968</t>
-  </si>
-  <si>
-    <t>amra90203@gmail.com</t>
-  </si>
-  <si>
-    <t>Ahmed amr farouk</t>
-  </si>
-  <si>
-    <t>2026-02-28 18:03</t>
-  </si>
-  <si>
-    <t>01094047162</t>
-  </si>
-  <si>
-    <t>samehsajeda1@gmail.com</t>
-  </si>
-  <si>
-    <t>ساجده سامح ياقوت</t>
-  </si>
-  <si>
-    <t>2026-02-28 18:02</t>
-  </si>
-  <si>
-    <t>01025448824</t>
-  </si>
-  <si>
-    <t>samaasker41@gmail.com</t>
-  </si>
-  <si>
-    <t>سما</t>
-  </si>
-  <si>
-    <t>2026-02-28 18:33</t>
-  </si>
-  <si>
-    <t>01122210707</t>
-  </si>
-  <si>
-    <t>lamaelshafay67@gmail.com</t>
-  </si>
-  <si>
-    <t>Hªnassameerh</t>
-  </si>
-  <si>
-    <t>2026-02-28 18:41</t>
-  </si>
-  <si>
-    <t>01096959817</t>
-  </si>
-  <si>
-    <t>ahmeddheshamm702@gmail.com</t>
-  </si>
-  <si>
-    <t>محمد هشام جلال</t>
-  </si>
-  <si>
-    <t>2026-02-28 18:36</t>
-  </si>
-  <si>
-    <t>01002426098</t>
-  </si>
-  <si>
-    <t>lujainmohamed194@gmail.com</t>
-  </si>
-  <si>
-    <t>لوجين محمد احمد عبدالغني</t>
-  </si>
-  <si>
-    <t>2026-02-28 19:15</t>
-  </si>
-  <si>
-    <t>01023257949</t>
-  </si>
-  <si>
-    <t>hamza.mohamed.hassan.8800@gmail.com</t>
-  </si>
-  <si>
-    <t>حمزة محمد حسن عبد المقصود</t>
-  </si>
-  <si>
-    <t>2026-02-28 19:17</t>
-  </si>
-  <si>
-    <t>01061456560</t>
-  </si>
-  <si>
-    <t>ahmedtiktok53@gmail.com</t>
-  </si>
-  <si>
-    <t>mariam abo el magd</t>
-  </si>
-  <si>
-    <t>2026-02-28 19:45</t>
-  </si>
-  <si>
-    <t>01125739890</t>
-  </si>
-  <si>
-    <t>oezzat626@gmail.com</t>
-  </si>
-  <si>
-    <t>Omar Mohammed Ezzat</t>
-  </si>
-  <si>
     <t>الحالة</t>
   </si>
   <si>
@@ -413,7 +410,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-01 12:08</t>
+    <t>تاريخ التصدير: 2026-03-01 12:31</t>
   </si>
 </sst>
 </file>
@@ -824,67 +821,67 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -892,19 +889,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G5" s="2">
         <v>6.0</v>
@@ -926,10 +923,10 @@
         <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>16.18</v>
+        <v>5.78</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>0</v>
@@ -940,47 +937,47 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="H6" s="2">
         <v>10.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J6" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2">
         <v>5</v>
       </c>
       <c r="N6" s="2">
-        <v>1.55</v>
+        <v>16.18</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -988,47 +985,47 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" s="2">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="H7" s="2">
         <v>10.0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="J7" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K7" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2">
         <v>5</v>
       </c>
       <c r="N7" s="2">
-        <v>9.5</v>
+        <v>1.55</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1036,13 +1033,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>3</v>
@@ -1057,7 +1054,7 @@
         <v>10.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J8" s="2">
         <v>4</v>
@@ -1070,10 +1067,10 @@
         <v>5</v>
       </c>
       <c r="N8" s="2">
-        <v>3.6</v>
+        <v>9.5</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>0</v>
@@ -1084,13 +1081,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>3</v>
@@ -1099,29 +1096,29 @@
         <v>1</v>
       </c>
       <c r="G9" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H9" s="2">
         <v>10.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J9" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K9" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2">
         <v>5</v>
       </c>
       <c r="N9" s="2">
-        <v>9.25</v>
+        <v>3.6</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>0</v>
@@ -1132,13 +1129,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>3</v>
@@ -1147,29 +1144,29 @@
         <v>1</v>
       </c>
       <c r="G10" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H10" s="2">
         <v>10.0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="J10" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K10" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2">
         <v>5</v>
       </c>
       <c r="N10" s="2">
-        <v>22.45</v>
+        <v>9.25</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>0</v>
@@ -1180,19 +1177,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F11" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" s="2">
         <v>8.0</v>
@@ -1201,7 +1198,7 @@
         <v>10.0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J11" s="2">
         <v>4</v>
@@ -1214,10 +1211,10 @@
         <v>5</v>
       </c>
       <c r="N11" s="2">
-        <v>4.3</v>
+        <v>22.45</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>0</v>
@@ -1228,19 +1225,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" s="2">
         <v>8.0</v>
@@ -1249,7 +1246,7 @@
         <v>10.0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J12" s="2">
         <v>4</v>
@@ -1262,10 +1259,10 @@
         <v>5</v>
       </c>
       <c r="N12" s="2">
-        <v>7.18</v>
+        <v>4.3</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>0</v>
@@ -1276,44 +1273,44 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F13" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H13" s="2">
         <v>10.0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J13" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K13" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2">
         <v>5</v>
       </c>
       <c r="N13" s="2">
-        <v>4.48</v>
+        <v>7.18</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>0</v>
@@ -1324,44 +1321,44 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F14" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G14" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H14" s="2">
         <v>10.0</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="J14" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K14" s="2">
         <v>2</v>
       </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N14" s="2">
-        <v>1.35</v>
+        <v>4.48</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>0</v>
@@ -1372,44 +1369,44 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F15" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G15" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H15" s="2">
         <v>10.0</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J15" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="2">
         <v>2</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N15" s="2">
-        <v>17.72</v>
+        <v>1.35</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>0</v>
@@ -1420,13 +1417,13 @@
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>3</v>
@@ -1454,10 +1451,10 @@
         <v>5</v>
       </c>
       <c r="N16" s="2">
-        <v>6.13</v>
+        <v>17.72</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>0</v>
@@ -1468,13 +1465,13 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>3</v>
@@ -1483,29 +1480,29 @@
         <v>1</v>
       </c>
       <c r="G17" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H17" s="2">
         <v>10.0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="J17" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K17" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2">
         <v>5</v>
       </c>
       <c r="N17" s="2">
-        <v>8.02</v>
+        <v>6.13</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>0</v>
@@ -1516,13 +1513,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>3</v>
@@ -1537,7 +1534,7 @@
         <v>10.0</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J18" s="2">
         <v>4</v>
@@ -1550,10 +1547,10 @@
         <v>5</v>
       </c>
       <c r="N18" s="2">
-        <v>26.88</v>
+        <v>8.02</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>0</v>
@@ -1564,47 +1561,47 @@
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F19" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19" s="2">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="H19" s="2">
         <v>10.0</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="J19" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K19" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2">
         <v>5</v>
       </c>
       <c r="N19" s="2">
-        <v>5.83</v>
+        <v>26.88</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -1612,47 +1609,47 @@
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F20" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="2">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="H20" s="2">
         <v>10.0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J20" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K20" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="2">
         <v>5</v>
       </c>
       <c r="N20" s="2">
-        <v>10.97</v>
+        <v>5.83</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -1660,19 +1657,19 @@
         <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F21" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G21" s="2">
         <v>6.0</v>
@@ -1694,10 +1691,10 @@
         <v>5</v>
       </c>
       <c r="N21" s="2">
-        <v>5.95</v>
+        <v>10.97</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>0</v>
@@ -1708,13 +1705,13 @@
         <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>3</v>
@@ -1742,10 +1739,10 @@
         <v>5</v>
       </c>
       <c r="N22" s="2">
-        <v>6.2</v>
+        <v>5.95</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>0</v>
@@ -1756,13 +1753,13 @@
         <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>3</v>
@@ -1771,32 +1768,32 @@
         <v>2</v>
       </c>
       <c r="G23" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="H23" s="2">
         <v>10.0</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J23" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" s="2">
         <v>5</v>
       </c>
       <c r="N23" s="2">
-        <v>5.78</v>
+        <v>6.2</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -1804,47 +1801,47 @@
         <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F24" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G24" s="2">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="H24" s="2">
         <v>10.0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="J24" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K24" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N24" s="2">
-        <v>124.4</v>
+        <v>5.78</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>34</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -1864,32 +1861,32 @@
         <v>3</v>
       </c>
       <c r="F25" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G25" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H25" s="2">
         <v>10.0</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J25" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K25" s="2">
         <v>2</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N25" s="2">
-        <v>5.03</v>
+        <v>124.4</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>0</v>
@@ -1900,13 +1897,13 @@
         <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>3</v>
@@ -1915,32 +1912,32 @@
         <v>2</v>
       </c>
       <c r="G26" s="2">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="H26" s="2">
         <v>10.0</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="J26" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K26" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" s="2">
         <v>5</v>
       </c>
       <c r="N26" s="2">
-        <v>4.33</v>
+        <v>5.03</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>25</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:16">

--- a/1_center.xlsx
+++ b/1_center.xlsx
@@ -410,7 +410,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-01 12:31</t>
+    <t>تاريخ التصدير: 2026-03-01 12:59</t>
   </si>
 </sst>
 </file>

--- a/1_center.xlsx
+++ b/1_center.xlsx
@@ -410,7 +410,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-01 13:03</t>
+    <t>تاريخ التصدير: 2026-03-01 13:18</t>
   </si>
 </sst>
 </file>

--- a/1_center.xlsx
+++ b/1_center.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="173">
   <si>
     <t>ناجح ✓</t>
   </si>
@@ -356,6 +356,129 @@
     <t>لوجين</t>
   </si>
   <si>
+    <t>2026-03-02 15:51</t>
+  </si>
+  <si>
+    <t>01122662621</t>
+  </si>
+  <si>
+    <t>shaymaa_amer@sci.asu.edu.eg</t>
+  </si>
+  <si>
+    <t>يوسف محمد محمود معوض</t>
+  </si>
+  <si>
+    <t>2026-03-05 13:55</t>
+  </si>
+  <si>
+    <t>01288179959</t>
+  </si>
+  <si>
+    <t>Halahisham203@gmail.com</t>
+  </si>
+  <si>
+    <t>Hala heshamm</t>
+  </si>
+  <si>
+    <t>2026-03-05 18:47</t>
+  </si>
+  <si>
+    <t>01552163162</t>
+  </si>
+  <si>
+    <t>sagdaashraf077@gmail.com</t>
+  </si>
+  <si>
+    <t>Sagda Ashraf</t>
+  </si>
+  <si>
+    <t>2026-03-05 20:17</t>
+  </si>
+  <si>
+    <t>01044248086</t>
+  </si>
+  <si>
+    <t>mahaghonim09@gmail.com</t>
+  </si>
+  <si>
+    <t>يحيي حسين عبدالحميد</t>
+  </si>
+  <si>
+    <t>2026-03-05 21:22</t>
+  </si>
+  <si>
+    <t>01032144322</t>
+  </si>
+  <si>
+    <t>nadernoureen977@gmail.com</t>
+  </si>
+  <si>
+    <t>Noureen</t>
+  </si>
+  <si>
+    <t>2026-03-06 02:07</t>
+  </si>
+  <si>
+    <t>100.0%</t>
+  </si>
+  <si>
+    <t>01080135152</t>
+  </si>
+  <si>
+    <t>Mazaki867@gmail.com</t>
+  </si>
+  <si>
+    <t>Mahmoud zaki abu alsooud</t>
+  </si>
+  <si>
+    <t>2026-03-06 09:47</t>
+  </si>
+  <si>
+    <t>01120913132</t>
+  </si>
+  <si>
+    <t>saharsaied.com@gmail.com</t>
+  </si>
+  <si>
+    <t>سهر سعبد رمضان</t>
+  </si>
+  <si>
+    <t>2026-03-06 11:50</t>
+  </si>
+  <si>
+    <t>01141701700</t>
+  </si>
+  <si>
+    <t>HazemKhleed098@gmail.com</t>
+  </si>
+  <si>
+    <t>حازم خالد جمال محمد</t>
+  </si>
+  <si>
+    <t>2026-03-06 13:12</t>
+  </si>
+  <si>
+    <t>01011501623</t>
+  </si>
+  <si>
+    <t>nour4sure@gmail.com</t>
+  </si>
+  <si>
+    <t>Nour El Dein hesham Mohammed</t>
+  </si>
+  <si>
+    <t>2026-03-06 13:16</t>
+  </si>
+  <si>
+    <t>01128133722</t>
+  </si>
+  <si>
+    <t>mohamedkhamis694000@gmail.com</t>
+  </si>
+  <si>
+    <t>Mohamed khamis refaay</t>
+  </si>
+  <si>
     <t>الحالة</t>
   </si>
   <si>
@@ -410,7 +533,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-01 13:18</t>
+    <t>تاريخ التصدير: 2026-03-06 13:35</t>
   </si>
 </sst>
 </file>
@@ -798,7 +921,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -821,67 +944,67 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
-        <v>129</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>131</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>127</v>
+        <v>168</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>126</v>
+        <v>167</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>125</v>
+        <v>166</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>122</v>
+        <v>163</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>120</v>
+        <v>161</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>119</v>
+        <v>160</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>118</v>
+        <v>159</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>117</v>
+        <v>158</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>116</v>
+        <v>157</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>115</v>
+        <v>156</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>114</v>
+        <v>155</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -889,44 +1012,42 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>112</v>
+        <v>153</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>111</v>
+        <v>152</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>110</v>
+        <v>151</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H5" s="2">
         <v>10.0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>2</v>
+        <v>134</v>
       </c>
       <c r="J5" s="2">
-        <v>3</v>
-      </c>
-      <c r="K5" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2">
         <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>5.78</v>
+        <v>3.47</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>0</v>
@@ -937,47 +1058,47 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>108</v>
+        <v>149</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="2">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="H6" s="2">
         <v>10.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J6" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K6" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2">
         <v>5</v>
       </c>
       <c r="N6" s="2">
-        <v>16.18</v>
+        <v>7.8</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -985,13 +1106,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>104</v>
+        <v>145</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>3</v>
@@ -1000,32 +1121,32 @@
         <v>2</v>
       </c>
       <c r="G7" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="H7" s="2">
         <v>10.0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J7" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2">
         <v>5</v>
       </c>
       <c r="N7" s="2">
-        <v>1.55</v>
+        <v>3.45</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1033,13 +1154,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>3</v>
@@ -1067,10 +1188,10 @@
         <v>5</v>
       </c>
       <c r="N8" s="2">
-        <v>9.5</v>
+        <v>4.1</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>0</v>
@@ -1081,44 +1202,42 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>95</v>
+        <v>136</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F9" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H9" s="2">
         <v>10.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>30</v>
+        <v>134</v>
       </c>
       <c r="J9" s="2">
-        <v>4</v>
-      </c>
-      <c r="K9" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2">
         <v>5</v>
       </c>
       <c r="N9" s="2">
-        <v>3.6</v>
+        <v>8.92</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>0</v>
@@ -1129,19 +1248,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>92</v>
+        <v>132</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>91</v>
+        <v>131</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F10" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" s="2">
         <v>6.0</v>
@@ -1163,10 +1282,10 @@
         <v>5</v>
       </c>
       <c r="N10" s="2">
-        <v>9.25</v>
+        <v>3.08</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>0</v>
@@ -1177,13 +1296,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>88</v>
+        <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>86</v>
+        <v>126</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>3</v>
@@ -1211,10 +1330,10 @@
         <v>5</v>
       </c>
       <c r="N11" s="2">
-        <v>22.45</v>
+        <v>4.75</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>0</v>
@@ -1225,19 +1344,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F12" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" s="2">
         <v>8.0</v>
@@ -1259,10 +1378,10 @@
         <v>5</v>
       </c>
       <c r="N12" s="2">
-        <v>4.3</v>
+        <v>9.8</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>0</v>
@@ -1273,44 +1392,44 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F13" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H13" s="2">
         <v>10.0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="J13" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K13" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2">
         <v>5</v>
       </c>
       <c r="N13" s="2">
-        <v>7.18</v>
+        <v>4.18</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>0</v>
@@ -1321,44 +1440,44 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>76</v>
+        <v>116</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F14" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H14" s="2">
         <v>10.0</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J14" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2">
         <v>5</v>
       </c>
       <c r="N14" s="2">
-        <v>4.48</v>
+        <v>6.45</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>0</v>
@@ -1369,44 +1488,44 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>73</v>
+        <v>112</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F15" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H15" s="2">
         <v>10.0</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="J15" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K15" s="2">
         <v>2</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N15" s="2">
-        <v>1.35</v>
+        <v>5.78</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>0</v>
@@ -1417,13 +1536,13 @@
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>67</v>
+        <v>106</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>3</v>
@@ -1451,10 +1570,10 @@
         <v>5</v>
       </c>
       <c r="N16" s="2">
-        <v>17.72</v>
+        <v>16.18</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>0</v>
@@ -1465,47 +1584,47 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>64</v>
+        <v>103</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F17" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" s="2">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="H17" s="2">
         <v>10.0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J17" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K17" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2">
         <v>5</v>
       </c>
       <c r="N17" s="2">
-        <v>6.13</v>
+        <v>1.55</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1513,13 +1632,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>3</v>
@@ -1547,10 +1666,10 @@
         <v>5</v>
       </c>
       <c r="N18" s="2">
-        <v>8.02</v>
+        <v>9.5</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>0</v>
@@ -1561,13 +1680,13 @@
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>3</v>
@@ -1595,10 +1714,10 @@
         <v>5</v>
       </c>
       <c r="N19" s="2">
-        <v>26.88</v>
+        <v>3.6</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>0</v>
@@ -1609,47 +1728,47 @@
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F20" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="H20" s="2">
         <v>10.0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J20" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K20" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="2">
         <v>5</v>
       </c>
       <c r="N20" s="2">
-        <v>5.83</v>
+        <v>9.25</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -1657,13 +1776,13 @@
         <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>3</v>
@@ -1672,29 +1791,29 @@
         <v>1</v>
       </c>
       <c r="G21" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H21" s="2">
         <v>10.0</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J21" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K21" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" s="2">
         <v>5</v>
       </c>
       <c r="N21" s="2">
-        <v>10.97</v>
+        <v>22.45</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>0</v>
@@ -1705,13 +1824,13 @@
         <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>3</v>
@@ -1720,29 +1839,29 @@
         <v>2</v>
       </c>
       <c r="G22" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H22" s="2">
         <v>10.0</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J22" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K22" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" s="2">
         <v>5</v>
       </c>
       <c r="N22" s="2">
-        <v>5.95</v>
+        <v>4.3</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>0</v>
@@ -1753,44 +1872,44 @@
         <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F23" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H23" s="2">
         <v>10.0</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J23" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K23" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" s="2">
         <v>5</v>
       </c>
       <c r="N23" s="2">
-        <v>6.2</v>
+        <v>7.18</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>0</v>
@@ -1801,13 +1920,13 @@
         <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>3</v>
@@ -1816,32 +1935,32 @@
         <v>2</v>
       </c>
       <c r="G24" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="H24" s="2">
         <v>10.0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J24" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K24" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" s="2">
         <v>5</v>
       </c>
       <c r="N24" s="2">
-        <v>5.78</v>
+        <v>4.48</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -1849,19 +1968,19 @@
         <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F25" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G25" s="2">
         <v>8.0</v>
@@ -1883,10 +2002,10 @@
         <v>6</v>
       </c>
       <c r="N25" s="2">
-        <v>124.4</v>
+        <v>1.35</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>0</v>
@@ -1897,19 +2016,19 @@
         <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F26" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" s="2">
         <v>6.0</v>
@@ -1931,10 +2050,10 @@
         <v>5</v>
       </c>
       <c r="N26" s="2">
-        <v>5.03</v>
+        <v>17.72</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>0</v>
@@ -1945,13 +2064,13 @@
         <v>23</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>3</v>
@@ -1979,10 +2098,10 @@
         <v>5</v>
       </c>
       <c r="N27" s="2">
-        <v>11.02</v>
+        <v>6.13</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>0</v>
@@ -1993,44 +2112,44 @@
         <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F28" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H28" s="2">
         <v>10.0</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J28" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K28" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" s="2">
         <v>5</v>
       </c>
       <c r="N28" s="2">
-        <v>12.1</v>
+        <v>8.02</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>0</v>
@@ -2041,13 +2160,13 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>3</v>
@@ -2056,29 +2175,29 @@
         <v>1</v>
       </c>
       <c r="G29" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H29" s="2">
         <v>10.0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J29" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K29" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" s="2">
         <v>5</v>
       </c>
       <c r="N29" s="2">
-        <v>16.07</v>
+        <v>26.88</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>0</v>
@@ -2089,13 +2208,13 @@
         <v>26</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>3</v>
@@ -2123,10 +2242,10 @@
         <v>5</v>
       </c>
       <c r="N30" s="2">
-        <v>5.67</v>
+        <v>5.83</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>7</v>
@@ -2137,13 +2256,13 @@
         <v>27</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>3</v>
@@ -2171,12 +2290,492 @@
         <v>5</v>
       </c>
       <c r="N31" s="2">
+        <v>10.97</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32" s="2">
+        <v>28</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="2">
+        <v>2</v>
+      </c>
+      <c r="G32" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H32" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J32" s="2">
+        <v>3</v>
+      </c>
+      <c r="K32" s="2">
+        <v>2</v>
+      </c>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2">
+        <v>5</v>
+      </c>
+      <c r="N32" s="2">
+        <v>5.95</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33" s="2">
+        <v>29</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F33" s="2">
+        <v>2</v>
+      </c>
+      <c r="G33" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H33" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J33" s="2">
+        <v>3</v>
+      </c>
+      <c r="K33" s="2">
+        <v>2</v>
+      </c>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2">
+        <v>5</v>
+      </c>
+      <c r="N33" s="2">
+        <v>6.2</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34" s="2">
+        <v>30</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F34" s="2">
+        <v>2</v>
+      </c>
+      <c r="G34" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="H34" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J34" s="2">
+        <v>2</v>
+      </c>
+      <c r="K34" s="2">
+        <v>3</v>
+      </c>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2">
+        <v>5</v>
+      </c>
+      <c r="N34" s="2">
+        <v>5.78</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="P34" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35" s="2">
+        <v>31</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F35" s="2">
+        <v>3</v>
+      </c>
+      <c r="G35" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H35" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J35" s="2">
+        <v>4</v>
+      </c>
+      <c r="K35" s="2">
+        <v>2</v>
+      </c>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2">
+        <v>6</v>
+      </c>
+      <c r="N35" s="2">
+        <v>124.4</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36" s="2">
+        <v>32</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F36" s="2">
+        <v>2</v>
+      </c>
+      <c r="G36" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H36" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J36" s="2">
+        <v>3</v>
+      </c>
+      <c r="K36" s="2">
+        <v>2</v>
+      </c>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2">
+        <v>5</v>
+      </c>
+      <c r="N36" s="2">
+        <v>5.03</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P36" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37" s="2">
+        <v>33</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F37" s="2">
+        <v>1</v>
+      </c>
+      <c r="G37" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H37" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J37" s="2">
+        <v>3</v>
+      </c>
+      <c r="K37" s="2">
+        <v>2</v>
+      </c>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2">
+        <v>5</v>
+      </c>
+      <c r="N37" s="2">
+        <v>11.02</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P37" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38" s="2">
+        <v>34</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F38" s="2">
+        <v>2</v>
+      </c>
+      <c r="G38" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H38" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J38" s="2">
+        <v>3</v>
+      </c>
+      <c r="K38" s="2">
+        <v>2</v>
+      </c>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2">
+        <v>5</v>
+      </c>
+      <c r="N38" s="2">
+        <v>12.1</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39" s="2">
+        <v>35</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H39" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J39" s="2">
+        <v>3</v>
+      </c>
+      <c r="K39" s="2">
+        <v>2</v>
+      </c>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2">
+        <v>5</v>
+      </c>
+      <c r="N39" s="2">
+        <v>16.07</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40" s="2">
+        <v>36</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F40" s="2">
+        <v>2</v>
+      </c>
+      <c r="G40" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="H40" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J40" s="2">
+        <v>2</v>
+      </c>
+      <c r="K40" s="2">
+        <v>3</v>
+      </c>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2">
+        <v>5</v>
+      </c>
+      <c r="N40" s="2">
+        <v>5.67</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41" s="2">
+        <v>37</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1</v>
+      </c>
+      <c r="G41" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H41" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J41" s="2">
+        <v>3</v>
+      </c>
+      <c r="K41" s="2">
+        <v>2</v>
+      </c>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2">
+        <v>5</v>
+      </c>
+      <c r="N41" s="2">
         <v>26.38</v>
       </c>
-      <c r="O31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P31" s="2" t="s">
+      <c r="O41" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P41" s="2" t="s">
         <v>0</v>
       </c>
     </row>

--- a/1_center.xlsx
+++ b/1_center.xlsx
@@ -533,7 +533,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-06 13:35</t>
+    <t>تاريخ التصدير: 2026-03-06 13:57</t>
   </si>
 </sst>
 </file>

--- a/1_center.xlsx
+++ b/1_center.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="189">
   <si>
     <t>ناجح ✓</t>
   </si>
@@ -284,7 +284,190 @@
     <t>Hªnassameerh</t>
   </si>
   <si>
-    <t>2026-02-28 18:41</t>
+    <t>2026-02-28 18:36</t>
+  </si>
+  <si>
+    <t>01002426098</t>
+  </si>
+  <si>
+    <t>lujainmohamed194@gmail.com</t>
+  </si>
+  <si>
+    <t>لوجين محمد احمد عبدالغني</t>
+  </si>
+  <si>
+    <t>2026-02-28 19:45</t>
+  </si>
+  <si>
+    <t>01125739890</t>
+  </si>
+  <si>
+    <t>oezzat626@gmail.com</t>
+  </si>
+  <si>
+    <t>Omar Mohammed Ezzat</t>
+  </si>
+  <si>
+    <t>2026-03-01 12:27</t>
+  </si>
+  <si>
+    <t>01507270279</t>
+  </si>
+  <si>
+    <t>lojywalied86@gmail.com</t>
+  </si>
+  <si>
+    <t>لوجين</t>
+  </si>
+  <si>
+    <t>2026-03-07 13:37</t>
+  </si>
+  <si>
+    <t>01061456560</t>
+  </si>
+  <si>
+    <t>ahmedtiktok53@gmail.com</t>
+  </si>
+  <si>
+    <t>mariam abo el magd</t>
+  </si>
+  <si>
+    <t>2026-03-02 15:51</t>
+  </si>
+  <si>
+    <t>01122662621</t>
+  </si>
+  <si>
+    <t>shaymaa_amer@sci.asu.edu.eg</t>
+  </si>
+  <si>
+    <t>يوسف محمد محمود معوض</t>
+  </si>
+  <si>
+    <t>2026-03-05 13:55</t>
+  </si>
+  <si>
+    <t>01288179959</t>
+  </si>
+  <si>
+    <t>Halahisham203@gmail.com</t>
+  </si>
+  <si>
+    <t>Hala heshamm</t>
+  </si>
+  <si>
+    <t>2026-03-05 18:47</t>
+  </si>
+  <si>
+    <t>01552163162</t>
+  </si>
+  <si>
+    <t>sagdaashraf077@gmail.com</t>
+  </si>
+  <si>
+    <t>Sagda Ashraf</t>
+  </si>
+  <si>
+    <t>2026-03-05 20:17</t>
+  </si>
+  <si>
+    <t>01044248086</t>
+  </si>
+  <si>
+    <t>mahaghonim09@gmail.com</t>
+  </si>
+  <si>
+    <t>يحيي حسين عبدالحميد</t>
+  </si>
+  <si>
+    <t>2026-03-05 21:22</t>
+  </si>
+  <si>
+    <t>01032144322</t>
+  </si>
+  <si>
+    <t>nadernoureen977@gmail.com</t>
+  </si>
+  <si>
+    <t>Noureen</t>
+  </si>
+  <si>
+    <t>2026-03-06 02:07</t>
+  </si>
+  <si>
+    <t>100.0%</t>
+  </si>
+  <si>
+    <t>01080135152</t>
+  </si>
+  <si>
+    <t>Mazaki867@gmail.com</t>
+  </si>
+  <si>
+    <t>Mahmoud zaki abu alsooud</t>
+  </si>
+  <si>
+    <t>2026-03-06 09:47</t>
+  </si>
+  <si>
+    <t>01120913132</t>
+  </si>
+  <si>
+    <t>saharsaied.com@gmail.com</t>
+  </si>
+  <si>
+    <t>سهر سعبد رمضان</t>
+  </si>
+  <si>
+    <t>2026-03-06 11:50</t>
+  </si>
+  <si>
+    <t>01141701700</t>
+  </si>
+  <si>
+    <t>HazemKhleed098@gmail.com</t>
+  </si>
+  <si>
+    <t>حازم خالد جمال محمد</t>
+  </si>
+  <si>
+    <t>2026-03-06 13:12</t>
+  </si>
+  <si>
+    <t>01011501623</t>
+  </si>
+  <si>
+    <t>nour4sure@gmail.com</t>
+  </si>
+  <si>
+    <t>Nour El Dein hesham Mohammed</t>
+  </si>
+  <si>
+    <t>2026-03-06 13:16</t>
+  </si>
+  <si>
+    <t>01128133722</t>
+  </si>
+  <si>
+    <t>mohamedkhamis694000@gmail.com</t>
+  </si>
+  <si>
+    <t>Mohamed khamis refaay</t>
+  </si>
+  <si>
+    <t>2026-03-06 17:51</t>
+  </si>
+  <si>
+    <t>01024258016</t>
+  </si>
+  <si>
+    <t>janaredaharhash@20008gmail.com</t>
+  </si>
+  <si>
+    <t>jana reda said</t>
+  </si>
+  <si>
+    <t>2026-03-07 14:50</t>
   </si>
   <si>
     <t>01096959817</t>
@@ -296,19 +479,31 @@
     <t>محمد هشام جلال</t>
   </si>
   <si>
-    <t>2026-02-28 18:36</t>
-  </si>
-  <si>
-    <t>01002426098</t>
-  </si>
-  <si>
-    <t>lujainmohamed194@gmail.com</t>
-  </si>
-  <si>
-    <t>لوجين محمد احمد عبدالغني</t>
-  </si>
-  <si>
-    <t>2026-02-28 19:15</t>
+    <t>2026-03-07 14:56</t>
+  </si>
+  <si>
+    <t>01050134045</t>
+  </si>
+  <si>
+    <t>hanamontaser22@gmail.com</t>
+  </si>
+  <si>
+    <t>هنا منتصر محمد</t>
+  </si>
+  <si>
+    <t>2026-03-07 15:57</t>
+  </si>
+  <si>
+    <t>01119290949</t>
+  </si>
+  <si>
+    <t>rorimohamed00@gmail.com</t>
+  </si>
+  <si>
+    <t>رنا محمد علي</t>
+  </si>
+  <si>
+    <t>2026-03-07 18:52</t>
   </si>
   <si>
     <t>01023257949</t>
@@ -320,163 +515,16 @@
     <t>حمزة محمد حسن عبد المقصود</t>
   </si>
   <si>
-    <t>2026-02-28 19:17</t>
-  </si>
-  <si>
-    <t>01061456560</t>
-  </si>
-  <si>
-    <t>ahmedtiktok53@gmail.com</t>
-  </si>
-  <si>
-    <t>mariam abo el magd</t>
-  </si>
-  <si>
-    <t>2026-02-28 19:45</t>
-  </si>
-  <si>
-    <t>01125739890</t>
-  </si>
-  <si>
-    <t>oezzat626@gmail.com</t>
-  </si>
-  <si>
-    <t>Omar Mohammed Ezzat</t>
-  </si>
-  <si>
-    <t>2026-03-01 12:27</t>
-  </si>
-  <si>
-    <t>01507270279</t>
-  </si>
-  <si>
-    <t>lojywalied86@gmail.com</t>
-  </si>
-  <si>
-    <t>لوجين</t>
-  </si>
-  <si>
-    <t>2026-03-02 15:51</t>
-  </si>
-  <si>
-    <t>01122662621</t>
-  </si>
-  <si>
-    <t>shaymaa_amer@sci.asu.edu.eg</t>
-  </si>
-  <si>
-    <t>يوسف محمد محمود معوض</t>
-  </si>
-  <si>
-    <t>2026-03-05 13:55</t>
-  </si>
-  <si>
-    <t>01288179959</t>
-  </si>
-  <si>
-    <t>Halahisham203@gmail.com</t>
-  </si>
-  <si>
-    <t>Hala heshamm</t>
-  </si>
-  <si>
-    <t>2026-03-05 18:47</t>
-  </si>
-  <si>
-    <t>01552163162</t>
-  </si>
-  <si>
-    <t>sagdaashraf077@gmail.com</t>
-  </si>
-  <si>
-    <t>Sagda Ashraf</t>
-  </si>
-  <si>
-    <t>2026-03-05 20:17</t>
-  </si>
-  <si>
-    <t>01044248086</t>
-  </si>
-  <si>
-    <t>mahaghonim09@gmail.com</t>
-  </si>
-  <si>
-    <t>يحيي حسين عبدالحميد</t>
-  </si>
-  <si>
-    <t>2026-03-05 21:22</t>
-  </si>
-  <si>
-    <t>01032144322</t>
-  </si>
-  <si>
-    <t>nadernoureen977@gmail.com</t>
-  </si>
-  <si>
-    <t>Noureen</t>
-  </si>
-  <si>
-    <t>2026-03-06 02:07</t>
-  </si>
-  <si>
-    <t>100.0%</t>
-  </si>
-  <si>
-    <t>01080135152</t>
-  </si>
-  <si>
-    <t>Mazaki867@gmail.com</t>
-  </si>
-  <si>
-    <t>Mahmoud zaki abu alsooud</t>
-  </si>
-  <si>
-    <t>2026-03-06 09:47</t>
-  </si>
-  <si>
-    <t>01120913132</t>
-  </si>
-  <si>
-    <t>saharsaied.com@gmail.com</t>
-  </si>
-  <si>
-    <t>سهر سعبد رمضان</t>
-  </si>
-  <si>
-    <t>2026-03-06 11:50</t>
-  </si>
-  <si>
-    <t>01141701700</t>
-  </si>
-  <si>
-    <t>HazemKhleed098@gmail.com</t>
-  </si>
-  <si>
-    <t>حازم خالد جمال محمد</t>
-  </si>
-  <si>
-    <t>2026-03-06 13:12</t>
-  </si>
-  <si>
-    <t>01011501623</t>
-  </si>
-  <si>
-    <t>nour4sure@gmail.com</t>
-  </si>
-  <si>
-    <t>Nour El Dein hesham Mohammed</t>
-  </si>
-  <si>
-    <t>2026-03-06 13:16</t>
-  </si>
-  <si>
-    <t>01128133722</t>
-  </si>
-  <si>
-    <t>mohamedkhamis694000@gmail.com</t>
-  </si>
-  <si>
-    <t>Mohamed khamis refaay</t>
+    <t>2026-03-07 19:28</t>
+  </si>
+  <si>
+    <t>01208754421</t>
+  </si>
+  <si>
+    <t>hanarania620@gmail.com</t>
+  </si>
+  <si>
+    <t>Hana amr mohamed</t>
   </si>
   <si>
     <t>الحالة</t>
@@ -533,7 +581,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-06 13:57</t>
+    <t>تاريخ التصدير: 2026-03-07 20:15</t>
   </si>
 </sst>
 </file>
@@ -921,7 +969,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:P45"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -944,67 +992,67 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1012,13 +1060,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>3</v>
@@ -1027,27 +1075,29 @@
         <v>1</v>
       </c>
       <c r="G5" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H5" s="2">
         <v>10.0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>134</v>
+        <v>2</v>
       </c>
       <c r="J5" s="2">
-        <v>5</v>
-      </c>
-      <c r="K5" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K5" s="2">
+        <v>2</v>
+      </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2">
         <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>3.47</v>
+        <v>2.82</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>0</v>
@@ -1058,13 +1108,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>3</v>
@@ -1073,32 +1123,32 @@
         <v>2</v>
       </c>
       <c r="G6" s="2">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="H6" s="2">
         <v>10.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="J6" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K6" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2">
         <v>5</v>
       </c>
       <c r="N6" s="2">
-        <v>7.8</v>
+        <v>9.18</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1106,44 +1156,44 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H7" s="2">
         <v>10.0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J7" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2">
         <v>5</v>
       </c>
       <c r="N7" s="2">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>0</v>
@@ -1154,13 +1204,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>3</v>
@@ -1169,29 +1219,27 @@
         <v>1</v>
       </c>
       <c r="G8" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H8" s="2">
         <v>10.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>30</v>
+        <v>126</v>
       </c>
       <c r="J8" s="2">
-        <v>4</v>
-      </c>
-      <c r="K8" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>0</v>
@@ -1202,13 +1250,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>3</v>
@@ -1217,30 +1265,32 @@
         <v>2</v>
       </c>
       <c r="G9" s="2">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="H9" s="2">
         <v>10.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>134</v>
+        <v>9</v>
       </c>
       <c r="J9" s="2">
-        <v>5</v>
-      </c>
-      <c r="K9" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="K9" s="2">
+        <v>3</v>
+      </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2">
         <v>5</v>
       </c>
       <c r="N9" s="2">
-        <v>8.92</v>
+        <v>1.12</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1248,44 +1298,44 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F10" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H10" s="2">
         <v>10.0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J10" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K10" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2">
         <v>5</v>
       </c>
       <c r="N10" s="2">
-        <v>3.08</v>
+        <v>8.47</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>0</v>
@@ -1296,44 +1346,42 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F11" s="2">
-        <v>1</v>
-      </c>
-      <c r="G11" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="H11" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="J11" s="2">
-        <v>4</v>
-      </c>
-      <c r="K11" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2">
         <v>5</v>
       </c>
       <c r="N11" s="2">
-        <v>4.75</v>
+        <v>3.47</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>0</v>
@@ -1344,47 +1392,47 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" s="2">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="H12" s="2">
         <v>10.0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="J12" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K12" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2">
         <v>5</v>
       </c>
       <c r="N12" s="2">
-        <v>9.8</v>
+        <v>7.8</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1392,13 +1440,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>3</v>
@@ -1426,10 +1474,10 @@
         <v>5</v>
       </c>
       <c r="N13" s="2">
-        <v>4.18</v>
+        <v>3.45</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>0</v>
@@ -1440,13 +1488,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>3</v>
@@ -1474,10 +1522,10 @@
         <v>5</v>
       </c>
       <c r="N14" s="2">
-        <v>6.45</v>
+        <v>4.1</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>0</v>
@@ -1488,44 +1536,42 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F15" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H15" s="2">
         <v>10.0</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>2</v>
+        <v>126</v>
       </c>
       <c r="J15" s="2">
-        <v>3</v>
-      </c>
-      <c r="K15" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2">
         <v>5</v>
       </c>
       <c r="N15" s="2">
-        <v>5.78</v>
+        <v>8.92</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>0</v>
@@ -1536,19 +1582,19 @@
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F16" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="2">
         <v>6.0</v>
@@ -1570,10 +1616,10 @@
         <v>5</v>
       </c>
       <c r="N16" s="2">
-        <v>16.18</v>
+        <v>3.08</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>0</v>
@@ -1584,47 +1630,47 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F17" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" s="2">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="H17" s="2">
         <v>10.0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="J17" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K17" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2">
         <v>5</v>
       </c>
       <c r="N17" s="2">
-        <v>1.55</v>
+        <v>4.75</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1632,13 +1678,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>3</v>
@@ -1666,10 +1712,10 @@
         <v>5</v>
       </c>
       <c r="N18" s="2">
-        <v>9.5</v>
+        <v>9.8</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>0</v>
@@ -1680,44 +1726,44 @@
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F19" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H19" s="2">
         <v>10.0</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="J19" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K19" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2">
         <v>5</v>
       </c>
       <c r="N19" s="2">
-        <v>3.6</v>
+        <v>4.18</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>0</v>
@@ -1728,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>3</v>
@@ -1743,29 +1789,29 @@
         <v>1</v>
       </c>
       <c r="G20" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H20" s="2">
         <v>10.0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J20" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K20" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="2">
         <v>5</v>
       </c>
       <c r="N20" s="2">
-        <v>9.25</v>
+        <v>6.45</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>0</v>
@@ -1776,19 +1822,19 @@
         <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F21" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G21" s="2">
         <v>8.0</v>
@@ -1810,10 +1856,10 @@
         <v>5</v>
       </c>
       <c r="N21" s="2">
-        <v>22.45</v>
+        <v>8715.42</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>0</v>
@@ -1824,44 +1870,44 @@
         <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F22" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H22" s="2">
         <v>10.0</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="J22" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K22" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" s="2">
         <v>5</v>
       </c>
       <c r="N22" s="2">
-        <v>4.3</v>
+        <v>5.78</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>0</v>
@@ -1872,13 +1918,13 @@
         <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>3</v>
@@ -1887,29 +1933,29 @@
         <v>1</v>
       </c>
       <c r="G23" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H23" s="2">
         <v>10.0</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="J23" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K23" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" s="2">
         <v>5</v>
       </c>
       <c r="N23" s="2">
-        <v>7.18</v>
+        <v>16.18</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>0</v>
@@ -1920,44 +1966,44 @@
         <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F24" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G24" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H24" s="2">
         <v>10.0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J24" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K24" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" s="2">
         <v>5</v>
       </c>
       <c r="N24" s="2">
-        <v>4.48</v>
+        <v>3.6</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>0</v>
@@ -1968,19 +2014,19 @@
         <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F25" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G25" s="2">
         <v>8.0</v>
@@ -1995,17 +2041,17 @@
         <v>4</v>
       </c>
       <c r="K25" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N25" s="2">
-        <v>1.35</v>
+        <v>22.45</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>0</v>
@@ -2016,44 +2062,44 @@
         <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F26" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H26" s="2">
         <v>10.0</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J26" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K26" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" s="2">
         <v>5</v>
       </c>
       <c r="N26" s="2">
-        <v>17.72</v>
+        <v>4.3</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>0</v>
@@ -2064,13 +2110,13 @@
         <v>23</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>3</v>
@@ -2079,29 +2125,29 @@
         <v>1</v>
       </c>
       <c r="G27" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H27" s="2">
         <v>10.0</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J27" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K27" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" s="2">
         <v>5</v>
       </c>
       <c r="N27" s="2">
-        <v>6.13</v>
+        <v>7.18</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>0</v>
@@ -2112,44 +2158,44 @@
         <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F28" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H28" s="2">
         <v>10.0</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="J28" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K28" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" s="2">
         <v>5</v>
       </c>
       <c r="N28" s="2">
-        <v>8.02</v>
+        <v>4.48</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>0</v>
@@ -2160,19 +2206,19 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F29" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G29" s="2">
         <v>8.0</v>
@@ -2187,17 +2233,17 @@
         <v>4</v>
       </c>
       <c r="K29" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N29" s="2">
-        <v>26.88</v>
+        <v>1.35</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>0</v>
@@ -2208,47 +2254,47 @@
         <v>26</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F30" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="H30" s="2">
         <v>10.0</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J30" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L30" s="2"/>
       <c r="M30" s="2">
         <v>5</v>
       </c>
       <c r="N30" s="2">
-        <v>5.83</v>
+        <v>17.72</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2256,13 +2302,13 @@
         <v>27</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>3</v>
@@ -2290,10 +2336,10 @@
         <v>5</v>
       </c>
       <c r="N31" s="2">
-        <v>10.97</v>
+        <v>6.13</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>0</v>
@@ -2304,44 +2350,44 @@
         <v>28</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F32" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H32" s="2">
         <v>10.0</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J32" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K32" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" s="2">
         <v>5</v>
       </c>
       <c r="N32" s="2">
-        <v>5.95</v>
+        <v>8.02</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>0</v>
@@ -2352,44 +2398,44 @@
         <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F33" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H33" s="2">
         <v>10.0</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J33" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K33" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" s="2">
         <v>5</v>
       </c>
       <c r="N33" s="2">
-        <v>6.2</v>
+        <v>26.88</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="P33" s="2" t="s">
         <v>0</v>
@@ -2400,13 +2446,13 @@
         <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>3</v>
@@ -2434,10 +2480,10 @@
         <v>5</v>
       </c>
       <c r="N34" s="2">
-        <v>5.78</v>
+        <v>5.83</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="P34" s="2" t="s">
         <v>7</v>
@@ -2448,44 +2494,44 @@
         <v>31</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F35" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G35" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H35" s="2">
         <v>10.0</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="J35" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K35" s="2">
         <v>2</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N35" s="2">
-        <v>124.4</v>
+        <v>10.97</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="P35" s="2" t="s">
         <v>0</v>
@@ -2496,13 +2542,13 @@
         <v>32</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>3</v>
@@ -2530,10 +2576,10 @@
         <v>5</v>
       </c>
       <c r="N36" s="2">
-        <v>5.03</v>
+        <v>5.95</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="P36" s="2" t="s">
         <v>0</v>
@@ -2544,19 +2590,19 @@
         <v>33</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F37" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G37" s="2">
         <v>6.0</v>
@@ -2578,10 +2624,10 @@
         <v>5</v>
       </c>
       <c r="N37" s="2">
-        <v>11.02</v>
+        <v>6.2</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="P37" s="2" t="s">
         <v>0</v>
@@ -2592,13 +2638,13 @@
         <v>34</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>3</v>
@@ -2607,32 +2653,32 @@
         <v>2</v>
       </c>
       <c r="G38" s="2">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="H38" s="2">
         <v>10.0</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J38" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K38" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" s="2">
         <v>5</v>
       </c>
       <c r="N38" s="2">
-        <v>12.1</v>
+        <v>5.78</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -2640,44 +2686,44 @@
         <v>35</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F39" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G39" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H39" s="2">
         <v>10.0</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J39" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K39" s="2">
         <v>2</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N39" s="2">
-        <v>16.07</v>
+        <v>124.4</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="P39" s="2" t="s">
         <v>0</v>
@@ -2688,13 +2734,13 @@
         <v>36</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>3</v>
@@ -2703,32 +2749,32 @@
         <v>2</v>
       </c>
       <c r="G40" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="H40" s="2">
         <v>10.0</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J40" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K40" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" s="2">
         <v>5</v>
       </c>
       <c r="N40" s="2">
-        <v>5.67</v>
+        <v>5.03</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -2736,13 +2782,13 @@
         <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>3</v>
@@ -2770,12 +2816,204 @@
         <v>5</v>
       </c>
       <c r="N41" s="2">
+        <v>11.02</v>
+      </c>
+      <c r="O41" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P41" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42" s="2">
+        <v>38</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F42" s="2">
+        <v>2</v>
+      </c>
+      <c r="G42" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H42" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J42" s="2">
+        <v>3</v>
+      </c>
+      <c r="K42" s="2">
+        <v>2</v>
+      </c>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2">
+        <v>5</v>
+      </c>
+      <c r="N42" s="2">
+        <v>12.1</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43" s="2">
+        <v>39</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H43" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J43" s="2">
+        <v>3</v>
+      </c>
+      <c r="K43" s="2">
+        <v>2</v>
+      </c>
+      <c r="L43" s="2"/>
+      <c r="M43" s="2">
+        <v>5</v>
+      </c>
+      <c r="N43" s="2">
+        <v>16.07</v>
+      </c>
+      <c r="O43" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P43" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44" s="2">
+        <v>40</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="2">
+        <v>2</v>
+      </c>
+      <c r="G44" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="H44" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J44" s="2">
+        <v>2</v>
+      </c>
+      <c r="K44" s="2">
+        <v>3</v>
+      </c>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2">
+        <v>5</v>
+      </c>
+      <c r="N44" s="2">
+        <v>5.67</v>
+      </c>
+      <c r="O44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P44" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45" s="2">
+        <v>41</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1</v>
+      </c>
+      <c r="G45" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H45" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J45" s="2">
+        <v>3</v>
+      </c>
+      <c r="K45" s="2">
+        <v>2</v>
+      </c>
+      <c r="L45" s="2"/>
+      <c r="M45" s="2">
+        <v>5</v>
+      </c>
+      <c r="N45" s="2">
         <v>26.38</v>
       </c>
-      <c r="O41" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P41" s="2" t="s">
+      <c r="O45" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P45" s="2" t="s">
         <v>0</v>
       </c>
     </row>

--- a/1_center.xlsx
+++ b/1_center.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="209">
   <si>
     <t>ناجح ✓</t>
   </si>
@@ -167,7 +167,148 @@
     <t>تقي محمد شحاته</t>
   </si>
   <si>
-    <t>2026-02-28 16:17</t>
+    <t>2026-02-28 17:02</t>
+  </si>
+  <si>
+    <t>01018664991</t>
+  </si>
+  <si>
+    <t>mohannadshaarawy1@gmail.com</t>
+  </si>
+  <si>
+    <t>Mohannad aly shaarawy</t>
+  </si>
+  <si>
+    <t>2026-02-28 16:46</t>
+  </si>
+  <si>
+    <t>01142590154</t>
+  </si>
+  <si>
+    <t>dok.mayarmahmoud@gmail.com</t>
+  </si>
+  <si>
+    <t>Mayar Mahmoud</t>
+  </si>
+  <si>
+    <t>2026-02-28 17:09</t>
+  </si>
+  <si>
+    <t>01552751484</t>
+  </si>
+  <si>
+    <t>saahnosa2010@gmail.com</t>
+  </si>
+  <si>
+    <t>سيف الدين احمد</t>
+  </si>
+  <si>
+    <t>2026-02-28 17:25</t>
+  </si>
+  <si>
+    <t>01202430665</t>
+  </si>
+  <si>
+    <t>alihatemyoussef58@gmail.com</t>
+  </si>
+  <si>
+    <t>Ali Hatem youssef</t>
+  </si>
+  <si>
+    <t>2026-02-28 17:22</t>
+  </si>
+  <si>
+    <t>01063145566</t>
+  </si>
+  <si>
+    <t>Hend95424@gmail.com</t>
+  </si>
+  <si>
+    <t>Hend Amr mohamed</t>
+  </si>
+  <si>
+    <t>01092299968</t>
+  </si>
+  <si>
+    <t>amra90203@gmail.com</t>
+  </si>
+  <si>
+    <t>Ahmed amr farouk</t>
+  </si>
+  <si>
+    <t>2026-02-28 18:03</t>
+  </si>
+  <si>
+    <t>01094047162</t>
+  </si>
+  <si>
+    <t>samehsajeda1@gmail.com</t>
+  </si>
+  <si>
+    <t>ساجده سامح ياقوت</t>
+  </si>
+  <si>
+    <t>2026-02-28 18:02</t>
+  </si>
+  <si>
+    <t>01025448824</t>
+  </si>
+  <si>
+    <t>samaasker41@gmail.com</t>
+  </si>
+  <si>
+    <t>سما</t>
+  </si>
+  <si>
+    <t>2026-02-28 18:33</t>
+  </si>
+  <si>
+    <t>01122210707</t>
+  </si>
+  <si>
+    <t>lamaelshafay67@gmail.com</t>
+  </si>
+  <si>
+    <t>Hªnassameerh</t>
+  </si>
+  <si>
+    <t>2026-02-28 18:36</t>
+  </si>
+  <si>
+    <t>01002426098</t>
+  </si>
+  <si>
+    <t>lujainmohamed194@gmail.com</t>
+  </si>
+  <si>
+    <t>لوجين محمد احمد عبدالغني</t>
+  </si>
+  <si>
+    <t>2026-02-28 19:45</t>
+  </si>
+  <si>
+    <t>01125739890</t>
+  </si>
+  <si>
+    <t>oezzat626@gmail.com</t>
+  </si>
+  <si>
+    <t>Omar Mohammed Ezzat</t>
+  </si>
+  <si>
+    <t>2026-03-01 12:27</t>
+  </si>
+  <si>
+    <t>01507270279</t>
+  </si>
+  <si>
+    <t>lojywalied86@gmail.com</t>
+  </si>
+  <si>
+    <t>لوجين</t>
+  </si>
+  <si>
+    <t>2026-03-14 17:54</t>
   </si>
   <si>
     <t>01065645606</t>
@@ -179,147 +320,6 @@
     <t>Mohamed Ahmed Naguib</t>
   </si>
   <si>
-    <t>2026-02-28 17:02</t>
-  </si>
-  <si>
-    <t>01018664991</t>
-  </si>
-  <si>
-    <t>mohannadshaarawy1@gmail.com</t>
-  </si>
-  <si>
-    <t>Mohannad aly shaarawy</t>
-  </si>
-  <si>
-    <t>2026-02-28 16:46</t>
-  </si>
-  <si>
-    <t>01142590154</t>
-  </si>
-  <si>
-    <t>dok.mayarmahmoud@gmail.com</t>
-  </si>
-  <si>
-    <t>Mayar Mahmoud</t>
-  </si>
-  <si>
-    <t>2026-02-28 17:09</t>
-  </si>
-  <si>
-    <t>01552751484</t>
-  </si>
-  <si>
-    <t>saahnosa2010@gmail.com</t>
-  </si>
-  <si>
-    <t>سيف الدين احمد</t>
-  </si>
-  <si>
-    <t>2026-02-28 17:25</t>
-  </si>
-  <si>
-    <t>01202430665</t>
-  </si>
-  <si>
-    <t>alihatemyoussef58@gmail.com</t>
-  </si>
-  <si>
-    <t>Ali Hatem youssef</t>
-  </si>
-  <si>
-    <t>2026-02-28 17:22</t>
-  </si>
-  <si>
-    <t>01063145566</t>
-  </si>
-  <si>
-    <t>Hend95424@gmail.com</t>
-  </si>
-  <si>
-    <t>Hend Amr mohamed</t>
-  </si>
-  <si>
-    <t>01092299968</t>
-  </si>
-  <si>
-    <t>amra90203@gmail.com</t>
-  </si>
-  <si>
-    <t>Ahmed amr farouk</t>
-  </si>
-  <si>
-    <t>2026-02-28 18:03</t>
-  </si>
-  <si>
-    <t>01094047162</t>
-  </si>
-  <si>
-    <t>samehsajeda1@gmail.com</t>
-  </si>
-  <si>
-    <t>ساجده سامح ياقوت</t>
-  </si>
-  <si>
-    <t>2026-02-28 18:02</t>
-  </si>
-  <si>
-    <t>01025448824</t>
-  </si>
-  <si>
-    <t>samaasker41@gmail.com</t>
-  </si>
-  <si>
-    <t>سما</t>
-  </si>
-  <si>
-    <t>2026-02-28 18:33</t>
-  </si>
-  <si>
-    <t>01122210707</t>
-  </si>
-  <si>
-    <t>lamaelshafay67@gmail.com</t>
-  </si>
-  <si>
-    <t>Hªnassameerh</t>
-  </si>
-  <si>
-    <t>2026-02-28 18:36</t>
-  </si>
-  <si>
-    <t>01002426098</t>
-  </si>
-  <si>
-    <t>lujainmohamed194@gmail.com</t>
-  </si>
-  <si>
-    <t>لوجين محمد احمد عبدالغني</t>
-  </si>
-  <si>
-    <t>2026-02-28 19:45</t>
-  </si>
-  <si>
-    <t>01125739890</t>
-  </si>
-  <si>
-    <t>oezzat626@gmail.com</t>
-  </si>
-  <si>
-    <t>Omar Mohammed Ezzat</t>
-  </si>
-  <si>
-    <t>2026-03-01 12:27</t>
-  </si>
-  <si>
-    <t>01507270279</t>
-  </si>
-  <si>
-    <t>lojywalied86@gmail.com</t>
-  </si>
-  <si>
-    <t>لوجين</t>
-  </si>
-  <si>
     <t>2026-03-07 13:37</t>
   </si>
   <si>
@@ -455,7 +455,115 @@
     <t>Mohamed khamis refaay</t>
   </si>
   <si>
-    <t>2026-03-06 17:51</t>
+    <t>2026-03-07 14:50</t>
+  </si>
+  <si>
+    <t>01096959817</t>
+  </si>
+  <si>
+    <t>ahmeddheshamm702@gmail.com</t>
+  </si>
+  <si>
+    <t>محمد هشام جلال</t>
+  </si>
+  <si>
+    <t>2026-03-07 14:56</t>
+  </si>
+  <si>
+    <t>01050134045</t>
+  </si>
+  <si>
+    <t>hanamontaser22@gmail.com</t>
+  </si>
+  <si>
+    <t>هنا منتصر محمد</t>
+  </si>
+  <si>
+    <t>2026-03-07 15:57</t>
+  </si>
+  <si>
+    <t>01119290949</t>
+  </si>
+  <si>
+    <t>rorimohamed00@gmail.com</t>
+  </si>
+  <si>
+    <t>رنا محمد علي</t>
+  </si>
+  <si>
+    <t>2026-03-07 18:52</t>
+  </si>
+  <si>
+    <t>01023257949</t>
+  </si>
+  <si>
+    <t>hamza.mohamed.hassan.8800@gmail.com</t>
+  </si>
+  <si>
+    <t>حمزة محمد حسن عبد المقصود</t>
+  </si>
+  <si>
+    <t>2026-03-07 19:28</t>
+  </si>
+  <si>
+    <t>01208754421</t>
+  </si>
+  <si>
+    <t>hanarania620@gmail.com</t>
+  </si>
+  <si>
+    <t>Hana amr mohamed</t>
+  </si>
+  <si>
+    <t>2026-03-09 09:57</t>
+  </si>
+  <si>
+    <t>01114191806</t>
+  </si>
+  <si>
+    <t>muhannad13209@gmail.com</t>
+  </si>
+  <si>
+    <t>مهند</t>
+  </si>
+  <si>
+    <t>2026-03-10 23:40</t>
+  </si>
+  <si>
+    <t>01118249020</t>
+  </si>
+  <si>
+    <t>y.k.ali2010@gmail.com</t>
+  </si>
+  <si>
+    <t>Yasmeen Khaled ali</t>
+  </si>
+  <si>
+    <t>2026-03-11 23:47</t>
+  </si>
+  <si>
+    <t>01270806310</t>
+  </si>
+  <si>
+    <t>2ndrewgaming@gmail.com</t>
+  </si>
+  <si>
+    <t>Andrew bassem</t>
+  </si>
+  <si>
+    <t>2026-03-13 12:32</t>
+  </si>
+  <si>
+    <t>01114373073</t>
+  </si>
+  <si>
+    <t>yoana.nabil64@gmail.com</t>
+  </si>
+  <si>
+    <t>يوأنا نبيل صبحي</t>
+  </si>
+  <si>
+    <t>2026-03-13 23:09</t>
   </si>
   <si>
     <t>01024258016</t>
@@ -467,64 +575,16 @@
     <t>jana reda said</t>
   </si>
   <si>
-    <t>2026-03-07 14:50</t>
-  </si>
-  <si>
-    <t>01096959817</t>
-  </si>
-  <si>
-    <t>ahmeddheshamm702@gmail.com</t>
-  </si>
-  <si>
-    <t>محمد هشام جلال</t>
-  </si>
-  <si>
-    <t>2026-03-07 14:56</t>
-  </si>
-  <si>
-    <t>01050134045</t>
-  </si>
-  <si>
-    <t>hanamontaser22@gmail.com</t>
-  </si>
-  <si>
-    <t>هنا منتصر محمد</t>
-  </si>
-  <si>
-    <t>2026-03-07 15:57</t>
-  </si>
-  <si>
-    <t>01119290949</t>
-  </si>
-  <si>
-    <t>rorimohamed00@gmail.com</t>
-  </si>
-  <si>
-    <t>رنا محمد علي</t>
-  </si>
-  <si>
-    <t>2026-03-07 18:52</t>
-  </si>
-  <si>
-    <t>01023257949</t>
-  </si>
-  <si>
-    <t>hamza.mohamed.hassan.8800@gmail.com</t>
-  </si>
-  <si>
-    <t>حمزة محمد حسن عبد المقصود</t>
-  </si>
-  <si>
-    <t>2026-03-07 19:28</t>
-  </si>
-  <si>
-    <t>01208754421</t>
-  </si>
-  <si>
-    <t>hanarania620@gmail.com</t>
-  </si>
-  <si>
-    <t>Hana amr mohamed</t>
+    <t>2026-03-14 17:01</t>
+  </si>
+  <si>
+    <t>01069466496</t>
+  </si>
+  <si>
+    <t>tarekismailahmedismailo@gmail.com</t>
+  </si>
+  <si>
+    <t>Tarek Ismail</t>
   </si>
   <si>
     <t>الحالة</t>
@@ -581,7 +641,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-07 20:15</t>
+    <t>تاريخ التصدير: 2026-03-14 19:05</t>
   </si>
 </sst>
 </file>
@@ -969,7 +1029,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P45"/>
+  <dimension ref="A1:P50"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -992,67 +1052,67 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1060,13 +1120,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>3</v>
@@ -1075,29 +1135,29 @@
         <v>1</v>
       </c>
       <c r="G5" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H5" s="2">
         <v>10.0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J5" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2">
         <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>2.82</v>
+        <v>4.48</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>0</v>
@@ -1108,13 +1168,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>3</v>
@@ -1142,10 +1202,10 @@
         <v>5</v>
       </c>
       <c r="N6" s="2">
-        <v>9.18</v>
+        <v>3.5</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>0</v>
@@ -1156,13 +1216,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>3</v>
@@ -1190,10 +1250,10 @@
         <v>5</v>
       </c>
       <c r="N7" s="2">
-        <v>3.8</v>
+        <v>14.02</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>0</v>
@@ -1204,13 +1264,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>3</v>
@@ -1219,27 +1279,29 @@
         <v>1</v>
       </c>
       <c r="G8" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H8" s="2">
         <v>10.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>126</v>
+        <v>30</v>
       </c>
       <c r="J8" s="2">
-        <v>5</v>
-      </c>
-      <c r="K8" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K8" s="2">
+        <v>1</v>
+      </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>0</v>
@@ -1250,47 +1312,47 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F9" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="H9" s="2">
         <v>10.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J9" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K9" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2">
         <v>5</v>
       </c>
       <c r="N9" s="2">
-        <v>1.12</v>
+        <v>4.2</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1298,13 +1360,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>3</v>
@@ -1313,29 +1375,29 @@
         <v>1</v>
       </c>
       <c r="G10" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H10" s="2">
         <v>10.0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="J10" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K10" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2">
         <v>5</v>
       </c>
       <c r="N10" s="2">
-        <v>8.47</v>
+        <v>3.48</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>0</v>
@@ -1346,13 +1408,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>3</v>
@@ -1361,27 +1423,29 @@
         <v>1</v>
       </c>
       <c r="G11" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H11" s="2">
         <v>10.0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>126</v>
+        <v>2</v>
       </c>
       <c r="J11" s="2">
-        <v>5</v>
-      </c>
-      <c r="K11" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K11" s="2">
+        <v>2</v>
+      </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2">
         <v>5</v>
       </c>
       <c r="N11" s="2">
-        <v>3.47</v>
+        <v>2.82</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>0</v>
@@ -1392,13 +1456,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>3</v>
@@ -1407,32 +1471,32 @@
         <v>2</v>
       </c>
       <c r="G12" s="2">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="H12" s="2">
         <v>10.0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="J12" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K12" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2">
         <v>5</v>
       </c>
       <c r="N12" s="2">
-        <v>7.8</v>
+        <v>9.18</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1440,44 +1504,44 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F13" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H13" s="2">
         <v>10.0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J13" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K13" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2">
         <v>5</v>
       </c>
       <c r="N13" s="2">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>0</v>
@@ -1488,13 +1552,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>3</v>
@@ -1503,29 +1567,27 @@
         <v>1</v>
       </c>
       <c r="G14" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H14" s="2">
         <v>10.0</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>30</v>
+        <v>126</v>
       </c>
       <c r="J14" s="2">
-        <v>4</v>
-      </c>
-      <c r="K14" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2">
         <v>5</v>
       </c>
       <c r="N14" s="2">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>0</v>
@@ -1536,13 +1598,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>3</v>
@@ -1551,30 +1613,32 @@
         <v>2</v>
       </c>
       <c r="G15" s="2">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="H15" s="2">
         <v>10.0</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>126</v>
+        <v>9</v>
       </c>
       <c r="J15" s="2">
-        <v>5</v>
-      </c>
-      <c r="K15" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="K15" s="2">
+        <v>3</v>
+      </c>
       <c r="L15" s="2"/>
       <c r="M15" s="2">
         <v>5</v>
       </c>
       <c r="N15" s="2">
-        <v>8.92</v>
+        <v>1.12</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1582,44 +1646,42 @@
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F16" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H16" s="2">
         <v>10.0</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>2</v>
+        <v>126</v>
       </c>
       <c r="J16" s="2">
-        <v>3</v>
-      </c>
-      <c r="K16" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2">
         <v>5</v>
       </c>
       <c r="N16" s="2">
-        <v>3.08</v>
+        <v>3.47</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>0</v>
@@ -1630,47 +1692,47 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F17" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" s="2">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="H17" s="2">
         <v>10.0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="J17" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K17" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2">
         <v>5</v>
       </c>
       <c r="N17" s="2">
-        <v>4.75</v>
+        <v>7.8</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1678,44 +1740,44 @@
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F18" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H18" s="2">
         <v>10.0</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="J18" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K18" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="2">
         <v>5</v>
       </c>
       <c r="N18" s="2">
-        <v>9.8</v>
+        <v>3.45</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>0</v>
@@ -1726,44 +1788,44 @@
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F19" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H19" s="2">
         <v>10.0</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J19" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K19" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2">
         <v>5</v>
       </c>
       <c r="N19" s="2">
-        <v>4.18</v>
+        <v>4.1</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>0</v>
@@ -1774,44 +1836,42 @@
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F20" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H20" s="2">
         <v>10.0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>30</v>
+        <v>126</v>
       </c>
       <c r="J20" s="2">
-        <v>4</v>
-      </c>
-      <c r="K20" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2">
         <v>5</v>
       </c>
       <c r="N20" s="2">
-        <v>6.45</v>
+        <v>8.92</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>0</v>
@@ -1822,44 +1882,44 @@
         <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F21" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G21" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H21" s="2">
         <v>10.0</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="J21" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K21" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" s="2">
         <v>5</v>
       </c>
       <c r="N21" s="2">
-        <v>8715.42</v>
+        <v>3.08</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>0</v>
@@ -1870,44 +1930,44 @@
         <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F22" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H22" s="2">
         <v>10.0</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J22" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K22" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" s="2">
         <v>5</v>
       </c>
       <c r="N22" s="2">
-        <v>5.78</v>
+        <v>4.75</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>0</v>
@@ -1918,13 +1978,13 @@
         <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>3</v>
@@ -1933,29 +1993,29 @@
         <v>1</v>
       </c>
       <c r="G23" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H23" s="2">
         <v>10.0</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J23" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K23" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" s="2">
         <v>5</v>
       </c>
       <c r="N23" s="2">
-        <v>16.18</v>
+        <v>9.8</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>0</v>
@@ -1966,44 +2026,44 @@
         <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F24" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H24" s="2">
         <v>10.0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="J24" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K24" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" s="2">
         <v>5</v>
       </c>
       <c r="N24" s="2">
-        <v>3.6</v>
+        <v>4.18</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>0</v>
@@ -2014,13 +2074,13 @@
         <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>3</v>
@@ -2048,10 +2108,10 @@
         <v>5</v>
       </c>
       <c r="N25" s="2">
-        <v>22.45</v>
+        <v>6.45</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>0</v>
@@ -2062,19 +2122,19 @@
         <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F26" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G26" s="2">
         <v>8.0</v>
@@ -2096,10 +2156,10 @@
         <v>5</v>
       </c>
       <c r="N26" s="2">
-        <v>4.3</v>
+        <v>8715.42</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>0</v>
@@ -2110,13 +2170,13 @@
         <v>23</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>3</v>
@@ -2144,10 +2204,10 @@
         <v>5</v>
       </c>
       <c r="N27" s="2">
-        <v>7.18</v>
+        <v>19053.23</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>0</v>
@@ -2158,19 +2218,19 @@
         <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F28" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" s="2">
         <v>6.0</v>
@@ -2192,10 +2252,10 @@
         <v>5</v>
       </c>
       <c r="N28" s="2">
-        <v>4.48</v>
+        <v>5.78</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>29</v>
+        <v>93</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>0</v>
@@ -2206,44 +2266,44 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F29" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G29" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H29" s="2">
         <v>10.0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="J29" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K29" s="2">
         <v>2</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N29" s="2">
-        <v>1.35</v>
+        <v>16.18</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>0</v>
@@ -2254,13 +2314,13 @@
         <v>26</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>3</v>
@@ -2269,29 +2329,29 @@
         <v>1</v>
       </c>
       <c r="G30" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H30" s="2">
         <v>10.0</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J30" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K30" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L30" s="2"/>
       <c r="M30" s="2">
         <v>5</v>
       </c>
       <c r="N30" s="2">
-        <v>17.72</v>
+        <v>3.6</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>0</v>
@@ -2302,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>3</v>
@@ -2317,29 +2377,29 @@
         <v>1</v>
       </c>
       <c r="G31" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H31" s="2">
         <v>10.0</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J31" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" s="2">
         <v>5</v>
       </c>
       <c r="N31" s="2">
-        <v>6.13</v>
+        <v>22.45</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>0</v>
@@ -2350,19 +2410,19 @@
         <v>28</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F32" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32" s="2">
         <v>8.0</v>
@@ -2384,10 +2444,10 @@
         <v>5</v>
       </c>
       <c r="N32" s="2">
-        <v>8.02</v>
+        <v>4.3</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>0</v>
@@ -2398,13 +2458,13 @@
         <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>3</v>
@@ -2432,10 +2492,10 @@
         <v>5</v>
       </c>
       <c r="N33" s="2">
-        <v>26.88</v>
+        <v>7.18</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="P33" s="2" t="s">
         <v>0</v>
@@ -2446,13 +2506,13 @@
         <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>3</v>
@@ -2461,32 +2521,32 @@
         <v>2</v>
       </c>
       <c r="G34" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="H34" s="2">
         <v>10.0</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J34" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K34" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" s="2">
         <v>5</v>
       </c>
       <c r="N34" s="2">
-        <v>5.83</v>
+        <v>4.48</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2494,44 +2554,44 @@
         <v>31</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F35" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G35" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H35" s="2">
         <v>10.0</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J35" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K35" s="2">
         <v>2</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N35" s="2">
-        <v>10.97</v>
+        <v>1.35</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="P35" s="2" t="s">
         <v>0</v>
@@ -2542,19 +2602,19 @@
         <v>32</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F36" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36" s="2">
         <v>6.0</v>
@@ -2576,10 +2636,10 @@
         <v>5</v>
       </c>
       <c r="N36" s="2">
-        <v>5.95</v>
+        <v>17.72</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="P36" s="2" t="s">
         <v>0</v>
@@ -2590,19 +2650,19 @@
         <v>33</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F37" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G37" s="2">
         <v>6.0</v>
@@ -2624,10 +2684,10 @@
         <v>5</v>
       </c>
       <c r="N37" s="2">
-        <v>6.2</v>
+        <v>6.13</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="P37" s="2" t="s">
         <v>0</v>
@@ -2638,47 +2698,47 @@
         <v>34</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F38" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G38" s="2">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="H38" s="2">
         <v>10.0</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="J38" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K38" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" s="2">
         <v>5</v>
       </c>
       <c r="N38" s="2">
-        <v>5.78</v>
+        <v>8.02</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -2686,19 +2746,19 @@
         <v>35</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F39" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G39" s="2">
         <v>8.0</v>
@@ -2713,17 +2773,17 @@
         <v>4</v>
       </c>
       <c r="K39" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N39" s="2">
-        <v>124.4</v>
+        <v>26.88</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="P39" s="2" t="s">
         <v>0</v>
@@ -2734,19 +2794,19 @@
         <v>36</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F40" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40" s="2">
         <v>6.0</v>
@@ -2768,10 +2828,10 @@
         <v>5</v>
       </c>
       <c r="N40" s="2">
-        <v>5.03</v>
+        <v>10.97</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="P40" s="2" t="s">
         <v>0</v>
@@ -2782,19 +2842,19 @@
         <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F41" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G41" s="2">
         <v>6.0</v>
@@ -2816,10 +2876,10 @@
         <v>5</v>
       </c>
       <c r="N41" s="2">
-        <v>11.02</v>
+        <v>5.95</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="P41" s="2" t="s">
         <v>0</v>
@@ -2830,13 +2890,13 @@
         <v>38</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>3</v>
@@ -2864,10 +2924,10 @@
         <v>5</v>
       </c>
       <c r="N42" s="2">
-        <v>12.1</v>
+        <v>6.2</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="P42" s="2" t="s">
         <v>0</v>
@@ -2878,47 +2938,47 @@
         <v>39</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F43" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G43" s="2">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="H43" s="2">
         <v>10.0</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J43" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K43" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" s="2">
         <v>5</v>
       </c>
       <c r="N43" s="2">
-        <v>16.07</v>
+        <v>5.78</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -2926,47 +2986,47 @@
         <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F44" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G44" s="2">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="H44" s="2">
         <v>10.0</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="J44" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K44" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N44" s="2">
-        <v>5.67</v>
+        <v>124.4</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -2974,19 +3034,19 @@
         <v>41</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F45" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G45" s="2">
         <v>6.0</v>
@@ -3008,12 +3068,252 @@
         <v>5</v>
       </c>
       <c r="N45" s="2">
+        <v>5.03</v>
+      </c>
+      <c r="O45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P45" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46" s="2">
+        <v>42</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H46" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J46" s="2">
+        <v>3</v>
+      </c>
+      <c r="K46" s="2">
+        <v>2</v>
+      </c>
+      <c r="L46" s="2"/>
+      <c r="M46" s="2">
+        <v>5</v>
+      </c>
+      <c r="N46" s="2">
+        <v>11.02</v>
+      </c>
+      <c r="O46" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P46" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47" s="2">
+        <v>43</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="2">
+        <v>2</v>
+      </c>
+      <c r="G47" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H47" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J47" s="2">
+        <v>3</v>
+      </c>
+      <c r="K47" s="2">
+        <v>2</v>
+      </c>
+      <c r="L47" s="2"/>
+      <c r="M47" s="2">
+        <v>5</v>
+      </c>
+      <c r="N47" s="2">
+        <v>12.1</v>
+      </c>
+      <c r="O47" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P47" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48" s="2">
+        <v>44</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1</v>
+      </c>
+      <c r="G48" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H48" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J48" s="2">
+        <v>3</v>
+      </c>
+      <c r="K48" s="2">
+        <v>2</v>
+      </c>
+      <c r="L48" s="2"/>
+      <c r="M48" s="2">
+        <v>5</v>
+      </c>
+      <c r="N48" s="2">
+        <v>16.07</v>
+      </c>
+      <c r="O48" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P48" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49" s="2">
+        <v>45</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F49" s="2">
+        <v>2</v>
+      </c>
+      <c r="G49" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="H49" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J49" s="2">
+        <v>2</v>
+      </c>
+      <c r="K49" s="2">
+        <v>3</v>
+      </c>
+      <c r="L49" s="2"/>
+      <c r="M49" s="2">
+        <v>5</v>
+      </c>
+      <c r="N49" s="2">
+        <v>5.67</v>
+      </c>
+      <c r="O49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P49" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50" s="2">
+        <v>46</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1</v>
+      </c>
+      <c r="G50" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H50" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J50" s="2">
+        <v>3</v>
+      </c>
+      <c r="K50" s="2">
+        <v>2</v>
+      </c>
+      <c r="L50" s="2"/>
+      <c r="M50" s="2">
+        <v>5</v>
+      </c>
+      <c r="N50" s="2">
         <v>26.38</v>
       </c>
-      <c r="O45" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P45" s="2" t="s">
+      <c r="O50" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P50" s="2" t="s">
         <v>0</v>
       </c>
     </row>

--- a/1_center.xlsx
+++ b/1_center.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="222">
   <si>
     <t>ناجح ✓</t>
   </si>
@@ -236,7 +236,370 @@
     <t>Ahmed amr farouk</t>
   </si>
   <si>
-    <t>2026-02-28 18:03</t>
+    <t>2026-02-28 18:02</t>
+  </si>
+  <si>
+    <t>01025448824</t>
+  </si>
+  <si>
+    <t>samaasker41@gmail.com</t>
+  </si>
+  <si>
+    <t>سما</t>
+  </si>
+  <si>
+    <t>2026-02-28 18:33</t>
+  </si>
+  <si>
+    <t>01122210707</t>
+  </si>
+  <si>
+    <t>lamaelshafay67@gmail.com</t>
+  </si>
+  <si>
+    <t>Hªnassameerh</t>
+  </si>
+  <si>
+    <t>2026-02-28 18:36</t>
+  </si>
+  <si>
+    <t>01002426098</t>
+  </si>
+  <si>
+    <t>lujainmohamed194@gmail.com</t>
+  </si>
+  <si>
+    <t>لوجين محمد احمد عبدالغني</t>
+  </si>
+  <si>
+    <t>2026-02-28 19:45</t>
+  </si>
+  <si>
+    <t>01125739890</t>
+  </si>
+  <si>
+    <t>oezzat626@gmail.com</t>
+  </si>
+  <si>
+    <t>Omar Mohammed Ezzat</t>
+  </si>
+  <si>
+    <t>2026-03-01 12:27</t>
+  </si>
+  <si>
+    <t>01507270279</t>
+  </si>
+  <si>
+    <t>lojywalied86@gmail.com</t>
+  </si>
+  <si>
+    <t>لوجين</t>
+  </si>
+  <si>
+    <t>2026-03-14 17:54</t>
+  </si>
+  <si>
+    <t>01065645606</t>
+  </si>
+  <si>
+    <t>mohamedahmednagib893@gamil.com</t>
+  </si>
+  <si>
+    <t>Mohamed Ahmed Naguib</t>
+  </si>
+  <si>
+    <t>2026-03-07 13:37</t>
+  </si>
+  <si>
+    <t>01061456560</t>
+  </si>
+  <si>
+    <t>ahmedtiktok53@gmail.com</t>
+  </si>
+  <si>
+    <t>mariam abo el magd</t>
+  </si>
+  <si>
+    <t>2026-03-02 15:51</t>
+  </si>
+  <si>
+    <t>01122662621</t>
+  </si>
+  <si>
+    <t>shaymaa_amer@sci.asu.edu.eg</t>
+  </si>
+  <si>
+    <t>يوسف محمد محمود معوض</t>
+  </si>
+  <si>
+    <t>2026-03-05 13:55</t>
+  </si>
+  <si>
+    <t>01288179959</t>
+  </si>
+  <si>
+    <t>Halahisham203@gmail.com</t>
+  </si>
+  <si>
+    <t>Hala heshamm</t>
+  </si>
+  <si>
+    <t>2026-03-05 18:47</t>
+  </si>
+  <si>
+    <t>01552163162</t>
+  </si>
+  <si>
+    <t>sagdaashraf077@gmail.com</t>
+  </si>
+  <si>
+    <t>Sagda Ashraf</t>
+  </si>
+  <si>
+    <t>2026-03-05 20:17</t>
+  </si>
+  <si>
+    <t>01044248086</t>
+  </si>
+  <si>
+    <t>mahaghonim09@gmail.com</t>
+  </si>
+  <si>
+    <t>يحيي حسين عبدالحميد</t>
+  </si>
+  <si>
+    <t>2026-03-05 21:22</t>
+  </si>
+  <si>
+    <t>01032144322</t>
+  </si>
+  <si>
+    <t>nadernoureen977@gmail.com</t>
+  </si>
+  <si>
+    <t>Noureen</t>
+  </si>
+  <si>
+    <t>2026-03-06 02:07</t>
+  </si>
+  <si>
+    <t>100.0%</t>
+  </si>
+  <si>
+    <t>01080135152</t>
+  </si>
+  <si>
+    <t>Mazaki867@gmail.com</t>
+  </si>
+  <si>
+    <t>Mahmoud zaki abu alsooud</t>
+  </si>
+  <si>
+    <t>2026-03-06 09:47</t>
+  </si>
+  <si>
+    <t>01120913132</t>
+  </si>
+  <si>
+    <t>saharsaied.com@gmail.com</t>
+  </si>
+  <si>
+    <t>سهر سعبد رمضان</t>
+  </si>
+  <si>
+    <t>2026-03-06 11:50</t>
+  </si>
+  <si>
+    <t>01141701700</t>
+  </si>
+  <si>
+    <t>HazemKhleed098@gmail.com</t>
+  </si>
+  <si>
+    <t>حازم خالد جمال محمد</t>
+  </si>
+  <si>
+    <t>2026-03-06 13:16</t>
+  </si>
+  <si>
+    <t>01128133722</t>
+  </si>
+  <si>
+    <t>mohamedkhamis694000@gmail.com</t>
+  </si>
+  <si>
+    <t>Mohamed khamis refaay</t>
+  </si>
+  <si>
+    <t>2026-03-07 14:50</t>
+  </si>
+  <si>
+    <t>01096959817</t>
+  </si>
+  <si>
+    <t>ahmeddheshamm702@gmail.com</t>
+  </si>
+  <si>
+    <t>محمد هشام جلال</t>
+  </si>
+  <si>
+    <t>2026-03-07 14:56</t>
+  </si>
+  <si>
+    <t>01050134045</t>
+  </si>
+  <si>
+    <t>hanamontaser22@gmail.com</t>
+  </si>
+  <si>
+    <t>هنا منتصر محمد</t>
+  </si>
+  <si>
+    <t>2026-03-07 15:57</t>
+  </si>
+  <si>
+    <t>01119290949</t>
+  </si>
+  <si>
+    <t>rorimohamed00@gmail.com</t>
+  </si>
+  <si>
+    <t>رنا محمد علي</t>
+  </si>
+  <si>
+    <t>2026-03-07 18:52</t>
+  </si>
+  <si>
+    <t>01023257949</t>
+  </si>
+  <si>
+    <t>hamza.mohamed.hassan.8800@gmail.com</t>
+  </si>
+  <si>
+    <t>حمزة محمد حسن عبد المقصود</t>
+  </si>
+  <si>
+    <t>2026-03-07 19:28</t>
+  </si>
+  <si>
+    <t>01208754421</t>
+  </si>
+  <si>
+    <t>hanarania620@gmail.com</t>
+  </si>
+  <si>
+    <t>Hana amr mohamed</t>
+  </si>
+  <si>
+    <t>2026-03-09 09:57</t>
+  </si>
+  <si>
+    <t>01114191806</t>
+  </si>
+  <si>
+    <t>muhannad13209@gmail.com</t>
+  </si>
+  <si>
+    <t>مهند</t>
+  </si>
+  <si>
+    <t>2026-03-10 23:40</t>
+  </si>
+  <si>
+    <t>01118249020</t>
+  </si>
+  <si>
+    <t>y.k.ali2010@gmail.com</t>
+  </si>
+  <si>
+    <t>Yasmeen Khaled ali</t>
+  </si>
+  <si>
+    <t>2026-03-11 23:47</t>
+  </si>
+  <si>
+    <t>01270806310</t>
+  </si>
+  <si>
+    <t>2ndrewgaming@gmail.com</t>
+  </si>
+  <si>
+    <t>Andrew bassem</t>
+  </si>
+  <si>
+    <t>2026-03-13 12:32</t>
+  </si>
+  <si>
+    <t>01114373073</t>
+  </si>
+  <si>
+    <t>yoana.nabil64@gmail.com</t>
+  </si>
+  <si>
+    <t>يوأنا نبيل صبحي</t>
+  </si>
+  <si>
+    <t>2026-03-13 23:09</t>
+  </si>
+  <si>
+    <t>01024258016</t>
+  </si>
+  <si>
+    <t>janaredaharhash@20008gmail.com</t>
+  </si>
+  <si>
+    <t>jana reda said</t>
+  </si>
+  <si>
+    <t>2026-03-27 23:16</t>
+  </si>
+  <si>
+    <t>01069466496</t>
+  </si>
+  <si>
+    <t>tarekismailahmedismailo@gmail.com</t>
+  </si>
+  <si>
+    <t>Tarek Ismail</t>
+  </si>
+  <si>
+    <t>2026-03-15 11:35</t>
+  </si>
+  <si>
+    <t>01022332743</t>
+  </si>
+  <si>
+    <t>malakk.elbanna@gmail.com</t>
+  </si>
+  <si>
+    <t>Malak Mohamed</t>
+  </si>
+  <si>
+    <t>2026-03-16 03:32</t>
+  </si>
+  <si>
+    <t>01011501623</t>
+  </si>
+  <si>
+    <t>nour4sure@gmail.com</t>
+  </si>
+  <si>
+    <t>Nour El Dein hesham Mohammed</t>
+  </si>
+  <si>
+    <t>2026-03-24 22:21</t>
+  </si>
+  <si>
+    <t>01141272319</t>
+  </si>
+  <si>
+    <t>mh799941@gmail.com</t>
+  </si>
+  <si>
+    <t>محمد حمدي حسين عماره</t>
+  </si>
+  <si>
+    <t>2026-03-24 23:41</t>
   </si>
   <si>
     <t>01094047162</t>
@@ -248,343 +611,19 @@
     <t>ساجده سامح ياقوت</t>
   </si>
   <si>
-    <t>2026-02-28 18:02</t>
-  </si>
-  <si>
-    <t>01025448824</t>
-  </si>
-  <si>
-    <t>samaasker41@gmail.com</t>
-  </si>
-  <si>
-    <t>سما</t>
-  </si>
-  <si>
-    <t>2026-02-28 18:33</t>
-  </si>
-  <si>
-    <t>01122210707</t>
-  </si>
-  <si>
-    <t>lamaelshafay67@gmail.com</t>
-  </si>
-  <si>
-    <t>Hªnassameerh</t>
-  </si>
-  <si>
-    <t>2026-02-28 18:36</t>
-  </si>
-  <si>
-    <t>01002426098</t>
-  </si>
-  <si>
-    <t>lujainmohamed194@gmail.com</t>
-  </si>
-  <si>
-    <t>لوجين محمد احمد عبدالغني</t>
-  </si>
-  <si>
-    <t>2026-02-28 19:45</t>
-  </si>
-  <si>
-    <t>01125739890</t>
-  </si>
-  <si>
-    <t>oezzat626@gmail.com</t>
-  </si>
-  <si>
-    <t>Omar Mohammed Ezzat</t>
-  </si>
-  <si>
-    <t>2026-03-01 12:27</t>
-  </si>
-  <si>
-    <t>01507270279</t>
-  </si>
-  <si>
-    <t>lojywalied86@gmail.com</t>
-  </si>
-  <si>
-    <t>لوجين</t>
-  </si>
-  <si>
-    <t>2026-03-14 17:54</t>
-  </si>
-  <si>
-    <t>01065645606</t>
-  </si>
-  <si>
-    <t>mohamedahmednagib893@gamil.com</t>
-  </si>
-  <si>
-    <t>Mohamed Ahmed Naguib</t>
-  </si>
-  <si>
-    <t>2026-03-07 13:37</t>
-  </si>
-  <si>
-    <t>01061456560</t>
-  </si>
-  <si>
-    <t>ahmedtiktok53@gmail.com</t>
-  </si>
-  <si>
-    <t>mariam abo el magd</t>
-  </si>
-  <si>
-    <t>2026-03-02 15:51</t>
-  </si>
-  <si>
-    <t>01122662621</t>
-  </si>
-  <si>
-    <t>shaymaa_amer@sci.asu.edu.eg</t>
-  </si>
-  <si>
-    <t>يوسف محمد محمود معوض</t>
-  </si>
-  <si>
-    <t>2026-03-05 13:55</t>
-  </si>
-  <si>
-    <t>01288179959</t>
-  </si>
-  <si>
-    <t>Halahisham203@gmail.com</t>
-  </si>
-  <si>
-    <t>Hala heshamm</t>
-  </si>
-  <si>
-    <t>2026-03-05 18:47</t>
-  </si>
-  <si>
-    <t>01552163162</t>
-  </si>
-  <si>
-    <t>sagdaashraf077@gmail.com</t>
-  </si>
-  <si>
-    <t>Sagda Ashraf</t>
-  </si>
-  <si>
-    <t>2026-03-05 20:17</t>
-  </si>
-  <si>
-    <t>01044248086</t>
-  </si>
-  <si>
-    <t>mahaghonim09@gmail.com</t>
-  </si>
-  <si>
-    <t>يحيي حسين عبدالحميد</t>
-  </si>
-  <si>
-    <t>2026-03-05 21:22</t>
-  </si>
-  <si>
-    <t>01032144322</t>
-  </si>
-  <si>
-    <t>nadernoureen977@gmail.com</t>
-  </si>
-  <si>
-    <t>Noureen</t>
-  </si>
-  <si>
-    <t>2026-03-06 02:07</t>
-  </si>
-  <si>
-    <t>100.0%</t>
-  </si>
-  <si>
-    <t>01080135152</t>
-  </si>
-  <si>
-    <t>Mazaki867@gmail.com</t>
-  </si>
-  <si>
-    <t>Mahmoud zaki abu alsooud</t>
-  </si>
-  <si>
-    <t>2026-03-06 09:47</t>
-  </si>
-  <si>
-    <t>01120913132</t>
-  </si>
-  <si>
-    <t>saharsaied.com@gmail.com</t>
-  </si>
-  <si>
-    <t>سهر سعبد رمضان</t>
-  </si>
-  <si>
-    <t>2026-03-06 11:50</t>
-  </si>
-  <si>
-    <t>01141701700</t>
-  </si>
-  <si>
-    <t>HazemKhleed098@gmail.com</t>
-  </si>
-  <si>
-    <t>حازم خالد جمال محمد</t>
-  </si>
-  <si>
-    <t>2026-03-06 13:12</t>
-  </si>
-  <si>
-    <t>01011501623</t>
-  </si>
-  <si>
-    <t>nour4sure@gmail.com</t>
-  </si>
-  <si>
-    <t>Nour El Dein hesham Mohammed</t>
-  </si>
-  <si>
-    <t>2026-03-06 13:16</t>
-  </si>
-  <si>
-    <t>01128133722</t>
-  </si>
-  <si>
-    <t>mohamedkhamis694000@gmail.com</t>
-  </si>
-  <si>
-    <t>Mohamed khamis refaay</t>
-  </si>
-  <si>
-    <t>2026-03-07 14:50</t>
-  </si>
-  <si>
-    <t>01096959817</t>
-  </si>
-  <si>
-    <t>ahmeddheshamm702@gmail.com</t>
-  </si>
-  <si>
-    <t>محمد هشام جلال</t>
-  </si>
-  <si>
-    <t>2026-03-07 14:56</t>
-  </si>
-  <si>
-    <t>01050134045</t>
-  </si>
-  <si>
-    <t>hanamontaser22@gmail.com</t>
-  </si>
-  <si>
-    <t>هنا منتصر محمد</t>
-  </si>
-  <si>
-    <t>2026-03-07 15:57</t>
-  </si>
-  <si>
-    <t>01119290949</t>
-  </si>
-  <si>
-    <t>rorimohamed00@gmail.com</t>
-  </si>
-  <si>
-    <t>رنا محمد علي</t>
-  </si>
-  <si>
-    <t>2026-03-07 18:52</t>
-  </si>
-  <si>
-    <t>01023257949</t>
-  </si>
-  <si>
-    <t>hamza.mohamed.hassan.8800@gmail.com</t>
-  </si>
-  <si>
-    <t>حمزة محمد حسن عبد المقصود</t>
-  </si>
-  <si>
-    <t>2026-03-07 19:28</t>
-  </si>
-  <si>
-    <t>01208754421</t>
-  </si>
-  <si>
-    <t>hanarania620@gmail.com</t>
-  </si>
-  <si>
-    <t>Hana amr mohamed</t>
-  </si>
-  <si>
-    <t>2026-03-09 09:57</t>
-  </si>
-  <si>
-    <t>01114191806</t>
-  </si>
-  <si>
-    <t>muhannad13209@gmail.com</t>
-  </si>
-  <si>
-    <t>مهند</t>
-  </si>
-  <si>
-    <t>2026-03-10 23:40</t>
-  </si>
-  <si>
-    <t>01118249020</t>
-  </si>
-  <si>
-    <t>y.k.ali2010@gmail.com</t>
-  </si>
-  <si>
-    <t>Yasmeen Khaled ali</t>
-  </si>
-  <si>
-    <t>2026-03-11 23:47</t>
-  </si>
-  <si>
-    <t>01270806310</t>
-  </si>
-  <si>
-    <t>2ndrewgaming@gmail.com</t>
-  </si>
-  <si>
-    <t>Andrew bassem</t>
-  </si>
-  <si>
-    <t>2026-03-13 12:32</t>
-  </si>
-  <si>
-    <t>01114373073</t>
-  </si>
-  <si>
-    <t>yoana.nabil64@gmail.com</t>
-  </si>
-  <si>
-    <t>يوأنا نبيل صبحي</t>
-  </si>
-  <si>
-    <t>2026-03-13 23:09</t>
-  </si>
-  <si>
-    <t>01024258016</t>
-  </si>
-  <si>
-    <t>janaredaharhash@20008gmail.com</t>
-  </si>
-  <si>
-    <t>jana reda said</t>
-  </si>
-  <si>
-    <t>2026-03-14 17:01</t>
-  </si>
-  <si>
-    <t>01069466496</t>
-  </si>
-  <si>
-    <t>tarekismailahmedismailo@gmail.com</t>
-  </si>
-  <si>
-    <t>Tarek Ismail</t>
+    <t>2026-04-03 02:10</t>
+  </si>
+  <si>
+    <t>20.0%</t>
+  </si>
+  <si>
+    <t>01094263555</t>
+  </si>
+  <si>
+    <t>ahmadhossam14@icloud.com</t>
+  </si>
+  <si>
+    <t>احمد حسام فتحي</t>
   </si>
   <si>
     <t>الحالة</t>
@@ -641,7 +680,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-14 19:05</t>
+    <t>تاريخ التصدير: 2026-04-03 13:54</t>
   </si>
 </sst>
 </file>
@@ -1029,7 +1068,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P50"/>
+  <dimension ref="A1:P53"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -1052,67 +1091,67 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1120,47 +1159,47 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="2">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="H5" s="2">
         <v>10.0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>30</v>
+        <v>199</v>
       </c>
       <c r="J5" s="2">
+        <v>1</v>
+      </c>
+      <c r="K5" s="2">
         <v>4</v>
-      </c>
-      <c r="K5" s="2">
-        <v>1</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2">
         <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>4.48</v>
+        <v>8.12</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1168,13 +1207,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>3</v>
@@ -1202,10 +1241,10 @@
         <v>5</v>
       </c>
       <c r="N6" s="2">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>0</v>
@@ -1216,13 +1255,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>3</v>
@@ -1231,29 +1270,27 @@
         <v>1</v>
       </c>
       <c r="G7" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H7" s="2">
         <v>10.0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>30</v>
+        <v>122</v>
       </c>
       <c r="J7" s="2">
-        <v>4</v>
-      </c>
-      <c r="K7" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2">
         <v>5</v>
       </c>
       <c r="N7" s="2">
-        <v>14.02</v>
+        <v>5.33</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>0</v>
@@ -1264,47 +1301,47 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F8" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G8" s="2">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="H8" s="2">
         <v>10.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="J8" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K8" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2">
-        <v>2.5</v>
+        <v>706.2</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1312,13 +1349,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>3</v>
@@ -1346,10 +1383,10 @@
         <v>5</v>
       </c>
       <c r="N9" s="2">
-        <v>4.2</v>
+        <v>4.98</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>0</v>
@@ -1360,19 +1397,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F10" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" s="2">
         <v>6.0</v>
@@ -1394,10 +1431,10 @@
         <v>5</v>
       </c>
       <c r="N10" s="2">
-        <v>3.48</v>
+        <v>19093.95</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>0</v>
@@ -1408,44 +1445,44 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F11" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H11" s="2">
         <v>10.0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J11" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K11" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2">
         <v>5</v>
       </c>
       <c r="N11" s="2">
-        <v>2.82</v>
+        <v>3.5</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>0</v>
@@ -1456,19 +1493,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F12" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" s="2">
         <v>8.0</v>
@@ -1490,10 +1527,10 @@
         <v>5</v>
       </c>
       <c r="N12" s="2">
-        <v>9.18</v>
+        <v>14.02</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>0</v>
@@ -1504,13 +1541,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>3</v>
@@ -1538,10 +1575,10 @@
         <v>5</v>
       </c>
       <c r="N13" s="2">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>0</v>
@@ -1552,13 +1589,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>3</v>
@@ -1567,27 +1604,29 @@
         <v>1</v>
       </c>
       <c r="G14" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H14" s="2">
         <v>10.0</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>126</v>
+        <v>2</v>
       </c>
       <c r="J14" s="2">
-        <v>5</v>
-      </c>
-      <c r="K14" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K14" s="2">
+        <v>2</v>
+      </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2">
         <v>5</v>
       </c>
       <c r="N14" s="2">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>0</v>
@@ -1598,47 +1637,47 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F15" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="H15" s="2">
         <v>10.0</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J15" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" s="2">
         <v>5</v>
       </c>
       <c r="N15" s="2">
-        <v>1.12</v>
+        <v>3.48</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1646,13 +1685,13 @@
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>3</v>
@@ -1661,27 +1700,29 @@
         <v>1</v>
       </c>
       <c r="G16" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H16" s="2">
         <v>10.0</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>126</v>
+        <v>2</v>
       </c>
       <c r="J16" s="2">
-        <v>5</v>
-      </c>
-      <c r="K16" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K16" s="2">
+        <v>2</v>
+      </c>
       <c r="L16" s="2"/>
       <c r="M16" s="2">
         <v>5</v>
       </c>
       <c r="N16" s="2">
-        <v>3.47</v>
+        <v>2.82</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>0</v>
@@ -1692,13 +1733,13 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>3</v>
@@ -1707,32 +1748,32 @@
         <v>2</v>
       </c>
       <c r="G17" s="2">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="H17" s="2">
         <v>10.0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="J17" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K17" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2">
         <v>5</v>
       </c>
       <c r="N17" s="2">
-        <v>7.8</v>
+        <v>9.18</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1740,44 +1781,44 @@
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F18" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H18" s="2">
         <v>10.0</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J18" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K18" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="2">
         <v>5</v>
       </c>
       <c r="N18" s="2">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>0</v>
@@ -1788,13 +1829,13 @@
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>3</v>
@@ -1803,29 +1844,27 @@
         <v>1</v>
       </c>
       <c r="G19" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H19" s="2">
         <v>10.0</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>30</v>
+        <v>122</v>
       </c>
       <c r="J19" s="2">
-        <v>4</v>
-      </c>
-      <c r="K19" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2">
         <v>5</v>
       </c>
       <c r="N19" s="2">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>0</v>
@@ -1836,13 +1875,13 @@
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>3</v>
@@ -1851,30 +1890,32 @@
         <v>2</v>
       </c>
       <c r="G20" s="2">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="H20" s="2">
         <v>10.0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>126</v>
+        <v>9</v>
       </c>
       <c r="J20" s="2">
-        <v>5</v>
-      </c>
-      <c r="K20" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="K20" s="2">
+        <v>3</v>
+      </c>
       <c r="L20" s="2"/>
       <c r="M20" s="2">
         <v>5</v>
       </c>
       <c r="N20" s="2">
-        <v>8.92</v>
+        <v>1.12</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -1882,44 +1923,42 @@
         <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H21" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F21" s="2">
-        <v>2</v>
-      </c>
-      <c r="G21" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="H21" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>2</v>
-      </c>
       <c r="J21" s="2">
-        <v>3</v>
-      </c>
-      <c r="K21" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K21" s="2"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2">
         <v>5</v>
       </c>
       <c r="N21" s="2">
-        <v>3.08</v>
+        <v>3.47</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>0</v>
@@ -1930,44 +1969,44 @@
         <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F22" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H22" s="2">
         <v>10.0</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="J22" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K22" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" s="2">
         <v>5</v>
       </c>
       <c r="N22" s="2">
-        <v>4.75</v>
+        <v>3.45</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>0</v>
@@ -1978,13 +2017,13 @@
         <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>3</v>
@@ -2012,10 +2051,10 @@
         <v>5</v>
       </c>
       <c r="N23" s="2">
-        <v>9.8</v>
+        <v>4.1</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>0</v>
@@ -2026,13 +2065,13 @@
         <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>3</v>
@@ -2041,29 +2080,27 @@
         <v>2</v>
       </c>
       <c r="G24" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H24" s="2">
         <v>10.0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>2</v>
+        <v>122</v>
       </c>
       <c r="J24" s="2">
-        <v>3</v>
-      </c>
-      <c r="K24" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2">
         <v>5</v>
       </c>
       <c r="N24" s="2">
-        <v>4.18</v>
+        <v>8.92</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>0</v>
@@ -2074,44 +2111,44 @@
         <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F25" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H25" s="2">
         <v>10.0</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="J25" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K25" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" s="2">
         <v>5</v>
       </c>
       <c r="N25" s="2">
-        <v>6.45</v>
+        <v>3.08</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>0</v>
@@ -2122,19 +2159,19 @@
         <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F26" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G26" s="2">
         <v>8.0</v>
@@ -2156,10 +2193,10 @@
         <v>5</v>
       </c>
       <c r="N26" s="2">
-        <v>8715.42</v>
+        <v>4.75</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>0</v>
@@ -2170,13 +2207,13 @@
         <v>23</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>3</v>
@@ -2204,10 +2241,10 @@
         <v>5</v>
       </c>
       <c r="N27" s="2">
-        <v>19053.23</v>
+        <v>9.8</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>0</v>
@@ -2218,19 +2255,19 @@
         <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F28" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" s="2">
         <v>6.0</v>
@@ -2252,10 +2289,10 @@
         <v>5</v>
       </c>
       <c r="N28" s="2">
-        <v>5.78</v>
+        <v>4.18</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>0</v>
@@ -2266,13 +2303,13 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>3</v>
@@ -2281,29 +2318,29 @@
         <v>1</v>
       </c>
       <c r="G29" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H29" s="2">
         <v>10.0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J29" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K29" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" s="2">
         <v>5</v>
       </c>
       <c r="N29" s="2">
-        <v>16.18</v>
+        <v>6.45</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>0</v>
@@ -2314,19 +2351,19 @@
         <v>26</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F30" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G30" s="2">
         <v>8.0</v>
@@ -2348,10 +2385,10 @@
         <v>5</v>
       </c>
       <c r="N30" s="2">
-        <v>3.6</v>
+        <v>8715.42</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>0</v>
@@ -2362,13 +2399,13 @@
         <v>27</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>3</v>
@@ -2396,10 +2433,10 @@
         <v>5</v>
       </c>
       <c r="N31" s="2">
-        <v>22.45</v>
+        <v>19053.23</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>0</v>
@@ -2410,44 +2447,44 @@
         <v>28</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F32" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G32" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H32" s="2">
         <v>10.0</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="J32" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K32" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" s="2">
         <v>5</v>
       </c>
       <c r="N32" s="2">
-        <v>4.3</v>
+        <v>5.78</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>0</v>
@@ -2458,13 +2495,13 @@
         <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>3</v>
@@ -2473,29 +2510,29 @@
         <v>1</v>
       </c>
       <c r="G33" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H33" s="2">
         <v>10.0</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="J33" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K33" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" s="2">
         <v>5</v>
       </c>
       <c r="N33" s="2">
-        <v>7.18</v>
+        <v>16.18</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="P33" s="2" t="s">
         <v>0</v>
@@ -2506,44 +2543,44 @@
         <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F34" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G34" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H34" s="2">
         <v>10.0</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J34" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K34" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" s="2">
         <v>5</v>
       </c>
       <c r="N34" s="2">
-        <v>4.48</v>
+        <v>3.6</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>29</v>
+        <v>81</v>
       </c>
       <c r="P34" s="2" t="s">
         <v>0</v>
@@ -2554,19 +2591,19 @@
         <v>31</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F35" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G35" s="2">
         <v>8.0</v>
@@ -2581,17 +2618,17 @@
         <v>4</v>
       </c>
       <c r="K35" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N35" s="2">
-        <v>1.35</v>
+        <v>22.45</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="P35" s="2" t="s">
         <v>0</v>
@@ -2602,44 +2639,44 @@
         <v>32</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F36" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H36" s="2">
         <v>10.0</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J36" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K36" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" s="2">
         <v>5</v>
       </c>
       <c r="N36" s="2">
-        <v>17.72</v>
+        <v>4.3</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="P36" s="2" t="s">
         <v>0</v>
@@ -2650,19 +2687,19 @@
         <v>33</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F37" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G37" s="2">
         <v>6.0</v>
@@ -2684,10 +2721,10 @@
         <v>5</v>
       </c>
       <c r="N37" s="2">
-        <v>6.13</v>
+        <v>4.48</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="P37" s="2" t="s">
         <v>0</v>
@@ -2698,19 +2735,19 @@
         <v>34</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F38" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G38" s="2">
         <v>8.0</v>
@@ -2725,17 +2762,17 @@
         <v>4</v>
       </c>
       <c r="K38" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N38" s="2">
-        <v>8.02</v>
+        <v>1.35</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>0</v>
@@ -2746,13 +2783,13 @@
         <v>35</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>3</v>
@@ -2761,29 +2798,29 @@
         <v>1</v>
       </c>
       <c r="G39" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H39" s="2">
         <v>10.0</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="J39" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K39" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" s="2">
         <v>5</v>
       </c>
       <c r="N39" s="2">
-        <v>26.88</v>
+        <v>17.72</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="P39" s="2" t="s">
         <v>0</v>
@@ -2794,13 +2831,13 @@
         <v>36</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>3</v>
@@ -2828,10 +2865,10 @@
         <v>5</v>
       </c>
       <c r="N40" s="2">
-        <v>10.97</v>
+        <v>6.13</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="P40" s="2" t="s">
         <v>0</v>
@@ -2842,44 +2879,44 @@
         <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F41" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G41" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H41" s="2">
         <v>10.0</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J41" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K41" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" s="2">
         <v>5</v>
       </c>
       <c r="N41" s="2">
-        <v>5.95</v>
+        <v>8.02</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="P41" s="2" t="s">
         <v>0</v>
@@ -2890,44 +2927,44 @@
         <v>38</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F42" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G42" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H42" s="2">
         <v>10.0</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J42" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K42" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2"/>
       <c r="M42" s="2">
         <v>5</v>
       </c>
       <c r="N42" s="2">
-        <v>6.2</v>
+        <v>26.88</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="P42" s="2" t="s">
         <v>0</v>
@@ -2938,47 +2975,47 @@
         <v>39</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F43" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="H43" s="2">
         <v>10.0</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J43" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K43" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" s="2">
         <v>5</v>
       </c>
       <c r="N43" s="2">
-        <v>5.78</v>
+        <v>10.97</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -2986,44 +3023,44 @@
         <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F44" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G44" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H44" s="2">
         <v>10.0</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="J44" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K44" s="2">
         <v>2</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N44" s="2">
-        <v>124.4</v>
+        <v>5.95</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="P44" s="2" t="s">
         <v>0</v>
@@ -3034,13 +3071,13 @@
         <v>41</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>3</v>
@@ -3068,10 +3105,10 @@
         <v>5</v>
       </c>
       <c r="N45" s="2">
-        <v>5.03</v>
+        <v>6.2</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="P45" s="2" t="s">
         <v>0</v>
@@ -3082,47 +3119,47 @@
         <v>42</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F46" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46" s="2">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="H46" s="2">
         <v>10.0</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J46" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K46" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" s="2">
         <v>5</v>
       </c>
       <c r="N46" s="2">
-        <v>11.02</v>
+        <v>5.78</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3130,44 +3167,44 @@
         <v>43</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F47" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G47" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H47" s="2">
         <v>10.0</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J47" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K47" s="2">
         <v>2</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N47" s="2">
-        <v>12.1</v>
+        <v>124.4</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="P47" s="2" t="s">
         <v>0</v>
@@ -3178,19 +3215,19 @@
         <v>44</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F48" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48" s="2">
         <v>6.0</v>
@@ -3212,10 +3249,10 @@
         <v>5</v>
       </c>
       <c r="N48" s="2">
-        <v>16.07</v>
+        <v>5.03</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="P48" s="2" t="s">
         <v>0</v>
@@ -3226,47 +3263,47 @@
         <v>45</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F49" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G49" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="H49" s="2">
         <v>10.0</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J49" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K49" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" s="2">
         <v>5</v>
       </c>
       <c r="N49" s="2">
-        <v>5.67</v>
+        <v>11.02</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3274,19 +3311,19 @@
         <v>46</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F50" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G50" s="2">
         <v>6.0</v>
@@ -3308,12 +3345,156 @@
         <v>5</v>
       </c>
       <c r="N50" s="2">
+        <v>12.1</v>
+      </c>
+      <c r="O50" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P50" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
+      <c r="A51" s="2">
+        <v>47</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F51" s="2">
+        <v>1</v>
+      </c>
+      <c r="G51" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H51" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J51" s="2">
+        <v>3</v>
+      </c>
+      <c r="K51" s="2">
+        <v>2</v>
+      </c>
+      <c r="L51" s="2"/>
+      <c r="M51" s="2">
+        <v>5</v>
+      </c>
+      <c r="N51" s="2">
+        <v>16.07</v>
+      </c>
+      <c r="O51" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P51" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
+      <c r="A52" s="2">
+        <v>48</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="2">
+        <v>2</v>
+      </c>
+      <c r="G52" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="H52" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J52" s="2">
+        <v>2</v>
+      </c>
+      <c r="K52" s="2">
+        <v>3</v>
+      </c>
+      <c r="L52" s="2"/>
+      <c r="M52" s="2">
+        <v>5</v>
+      </c>
+      <c r="N52" s="2">
+        <v>5.67</v>
+      </c>
+      <c r="O52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P52" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
+      <c r="A53" s="2">
+        <v>49</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F53" s="2">
+        <v>1</v>
+      </c>
+      <c r="G53" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H53" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J53" s="2">
+        <v>3</v>
+      </c>
+      <c r="K53" s="2">
+        <v>2</v>
+      </c>
+      <c r="L53" s="2"/>
+      <c r="M53" s="2">
+        <v>5</v>
+      </c>
+      <c r="N53" s="2">
         <v>26.38</v>
       </c>
-      <c r="O50" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P50" s="2" t="s">
+      <c r="O53" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P53" s="2" t="s">
         <v>0</v>
       </c>
     </row>

--- a/1_center.xlsx
+++ b/1_center.xlsx
@@ -680,7 +680,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-04-03 13:54</t>
+    <t>تاريخ التصدير: 2026-04-04 16:47</t>
   </si>
 </sst>
 </file>
